--- a/Archived_HE_Data/hedata_2026-08-11.xlsx
+++ b/Archived_HE_Data/hedata_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="952">
   <si>
     <t>Title</t>
   </si>
@@ -34,6 +34,39 @@
     <t>Archive_Date</t>
   </si>
   <si>
+    <t>Accounts Payable Manager</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>Montana State University</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52557</t>
+  </si>
+  <si>
+    <t>Composite Research Engineer</t>
+  </si>
+  <si>
+    <t>Mechanical &amp; Industrial Engineering</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52555</t>
+  </si>
+  <si>
+    <t>Registered Dietitian Nutritionist</t>
+  </si>
+  <si>
+    <t>Athletics</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52554</t>
+  </si>
+  <si>
     <t>Administrative Associate IV, Buffalo Nations</t>
   </si>
   <si>
@@ -43,30 +76,9 @@
     <t>2026-08-10</t>
   </si>
   <si>
-    <t>Montana State University</t>
-  </si>
-  <si>
     <t>https://jobs.montana.edu/postings/52548</t>
   </si>
   <si>
-    <t>Registered Dietitian Nutritionist</t>
-  </si>
-  <si>
-    <t>Athletics</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52544</t>
-  </si>
-  <si>
-    <t>Composite Research Engineer</t>
-  </si>
-  <si>
-    <t>Mechanical &amp; Industrial Engineering</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52540</t>
-  </si>
-  <si>
     <t>Graphic Designer</t>
   </si>
   <si>
@@ -610,18 +622,6 @@
     <t>https://jobs.montana.edu/postings/52244</t>
   </si>
   <si>
-    <t>Operations Specialist</t>
-  </si>
-  <si>
-    <t>Brick Breeden Fieldhouse</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52228</t>
-  </si>
-  <si>
     <t>Administrative Associate III</t>
   </si>
   <si>
@@ -706,18 +706,6 @@
     <t>https://jobs.montana.edu/postings/52121</t>
   </si>
   <si>
-    <t>Program and Finance Manager</t>
-  </si>
-  <si>
-    <t>NSF EPSCOR</t>
-  </si>
-  <si>
-    <t>2026-07-06</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52114</t>
-  </si>
-  <si>
     <t>HDCH Non-Tenure Track Faculty (Applicant Pool)</t>
   </si>
   <si>
@@ -769,24 +757,15 @@
     <t>https://jobs.montana.edu/postings/52049</t>
   </si>
   <si>
-    <t>Accounts Payable Manager</t>
-  </si>
-  <si>
-    <t>Controller</t>
+    <t>College of Nursing Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Nursing Departments</t>
   </si>
   <si>
     <t>2026-06-29</t>
   </si>
   <si>
-    <t>https://jobs.montana.edu/postings/52042</t>
-  </si>
-  <si>
-    <t>College of Nursing Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Nursing Departments</t>
-  </si>
-  <si>
     <t>https://jobs.montana.edu/postings/52040</t>
   </si>
   <si>
@@ -1780,27 +1759,27 @@
     <t>https://jobs.msun.edu/postings/2629</t>
   </si>
   <si>
+    <t>Director of Workforce Operations (INTERNAL ONLY)</t>
+  </si>
+  <si>
+    <t>CTE/Health Sciences</t>
+  </si>
+  <si>
+    <t>Great Falls College MSU</t>
+  </si>
+  <si>
+    <t>https://jobs.gfcmsu.edu/postings/2547</t>
+  </si>
+  <si>
     <t>Early Learning Center Teachers</t>
   </si>
   <si>
     <t>Office of Administration &amp; Finance</t>
   </si>
   <si>
-    <t>Great Falls College MSU</t>
-  </si>
-  <si>
     <t>https://jobs.gfcmsu.edu/postings/2546</t>
   </si>
   <si>
-    <t>Director of Workforce Operations</t>
-  </si>
-  <si>
-    <t>CTE/Health Sciences</t>
-  </si>
-  <si>
-    <t>https://jobs.gfcmsu.edu/postings/2543</t>
-  </si>
-  <si>
     <t>Health Sciences Program Site Coordinator</t>
   </si>
   <si>
@@ -1984,6 +1963,12 @@
     <t>https://montanatechuniversity.applytojob.com/apply/AXgZ48saLG/Interdisciplinary-Postdoctoral-Opportunities-Open-Pool</t>
   </si>
   <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>https://montanatechuniversity.applytojob.com/apply/FobdfWCi4X/Program-Manager</t>
+  </si>
+  <si>
     <t>Upward Bound/Upward Bound Math &amp; Science Coordinator</t>
   </si>
   <si>
@@ -2506,6 +2491,12 @@
     <t>https://www.schooljobs.com/careers/ummissoula/jobs/5428240/manager-of-events-marketing-and-communications-mansfield-center</t>
   </si>
   <si>
+    <t>Occupational Health and Safety Technician, Environmental Health and Safety</t>
+  </si>
+  <si>
+    <t>https://www.schooljobs.com/careers/ummissoula/jobs/5443696/occupational-health-and-safety-technician-environmental-health-and-safety</t>
+  </si>
+  <si>
     <t>Pollinator Survey Assistant, Center for Integrated Research on the Environment</t>
   </si>
   <si>
@@ -2714,9 +2705,6 @@
   </si>
   <si>
     <t>Accounting Assistant</t>
-  </si>
-  <si>
-    <t>Pre-Engineering/Physics Faculty and Digital Manufacturing Lab Director</t>
   </si>
   <si>
     <t>Tribal Research &amp; Education in Ecosystem Sciences (TREES) Center Director</t>
@@ -3228,7 +3216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F374"/>
+  <dimension ref="A1:F373"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="1" customWidth="1"/>
@@ -3322,13 +3310,13 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1">
         <v>46245</v>
@@ -3336,19 +3324,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1">
         <v>46245</v>
@@ -3356,13 +3344,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
@@ -3382,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" s="1">
         <v>46245</v>
@@ -3396,13 +3384,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -3422,13 +3410,13 @@
         <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" s="1">
         <v>46245</v>
@@ -3436,19 +3424,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F11" s="1">
         <v>46245</v>
@@ -3456,13 +3444,13 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
@@ -3482,13 +3470,13 @@
         <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F13" s="1">
         <v>46245</v>
@@ -3496,19 +3484,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F14" s="1">
         <v>46245</v>
@@ -3516,13 +3504,13 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
@@ -3542,13 +3530,13 @@
         <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F16" s="1">
         <v>46245</v>
@@ -3556,19 +3544,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F17" s="1">
         <v>46245</v>
@@ -3576,19 +3564,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F18" s="1">
         <v>46245</v>
@@ -3596,19 +3584,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F19" s="1">
         <v>46245</v>
@@ -3616,19 +3604,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F20" s="1">
         <v>46245</v>
@@ -3636,19 +3624,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
         <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F21" s="1">
         <v>46245</v>
@@ -3656,19 +3644,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F22" s="1">
         <v>46245</v>
@@ -3676,19 +3664,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F23" s="1">
         <v>46245</v>
@@ -3696,19 +3684,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F24" s="1">
         <v>46245</v>
@@ -3716,19 +3704,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F25" s="1">
         <v>46245</v>
@@ -3736,13 +3724,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
         <v>9</v>
@@ -3762,13 +3750,13 @@
         <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F27" s="1">
         <v>46245</v>
@@ -3776,19 +3764,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F28" s="1">
         <v>46245</v>
@@ -3796,19 +3784,19 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F29" s="1">
         <v>46245</v>
@@ -3816,19 +3804,19 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F30" s="1">
         <v>46245</v>
@@ -3836,19 +3824,19 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F31" s="1">
         <v>46245</v>
@@ -3856,10 +3844,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s">
         <v>104</v>
@@ -3882,13 +3870,13 @@
         <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F33" s="1">
         <v>46245</v>
@@ -3896,19 +3884,19 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F34" s="1">
         <v>46245</v>
@@ -3916,13 +3904,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
@@ -3942,13 +3930,13 @@
         <v>117</v>
       </c>
       <c r="C36" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F36" s="1">
         <v>46245</v>
@@ -3956,19 +3944,19 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F37" s="1">
         <v>46245</v>
@@ -3976,19 +3964,19 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="C38" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F38" s="1">
         <v>46245</v>
@@ -3996,19 +3984,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F39" s="1">
         <v>46245</v>
@@ -4016,19 +4004,19 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F40" s="1">
         <v>46245</v>
@@ -4036,19 +4024,19 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F41" s="1">
         <v>46245</v>
@@ -4056,19 +4044,19 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D42" t="s">
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F42" s="1">
         <v>46245</v>
@@ -4076,10 +4064,10 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
         <v>135</v>
@@ -4102,13 +4090,13 @@
         <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
         <v>9</v>
       </c>
       <c r="E44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F44" s="1">
         <v>46245</v>
@@ -4116,19 +4104,19 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="C45" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D45" t="s">
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F45" s="1">
         <v>46245</v>
@@ -4136,19 +4124,19 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D46" t="s">
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F46" s="1">
         <v>46245</v>
@@ -4156,19 +4144,19 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D47" t="s">
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F47" s="1">
         <v>46245</v>
@@ -4176,19 +4164,19 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B48" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="C48" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D48" t="s">
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F48" s="1">
         <v>46245</v>
@@ -4196,19 +4184,19 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D49" t="s">
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F49" s="1">
         <v>46245</v>
@@ -4216,19 +4204,19 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>156</v>
       </c>
       <c r="C50" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D50" t="s">
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F50" s="1">
         <v>46245</v>
@@ -4236,19 +4224,19 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B51" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D51" t="s">
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F51" s="1">
         <v>46245</v>
@@ -4256,19 +4244,19 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B52" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C52" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D52" t="s">
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F52" s="1">
         <v>46245</v>
@@ -4276,19 +4264,19 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B53" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C53" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D53" t="s">
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F53" s="1">
         <v>46245</v>
@@ -4296,19 +4284,19 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54" t="s">
         <v>165</v>
       </c>
-      <c r="B54" t="s">
-        <v>166</v>
-      </c>
       <c r="C54" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D54" t="s">
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F54" s="1">
         <v>46245</v>
@@ -4316,19 +4304,19 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B55" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C55" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D55" t="s">
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F55" s="1">
         <v>46245</v>
@@ -4336,13 +4324,13 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" t="s">
         <v>170</v>
       </c>
-      <c r="B56" t="s">
-        <v>171</v>
-      </c>
       <c r="C56" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="D56" t="s">
         <v>9</v>
@@ -4356,19 +4344,19 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="C57" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D57" t="s">
         <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F57" s="1">
         <v>46245</v>
@@ -4376,13 +4364,13 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="B58" t="s">
+        <v>121</v>
+      </c>
+      <c r="C58" t="s">
         <v>176</v>
-      </c>
-      <c r="C58" t="s">
-        <v>177</v>
       </c>
       <c r="D58" t="s">
         <v>9</v>
@@ -4422,13 +4410,13 @@
         <v>184</v>
       </c>
       <c r="C60" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D60" t="s">
         <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F60" s="1">
         <v>46245</v>
@@ -4436,19 +4424,19 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B61" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="C61" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D61" t="s">
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F61" s="1">
         <v>46245</v>
@@ -4456,19 +4444,19 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B62" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C62" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D62" t="s">
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F62" s="1">
         <v>46245</v>
@@ -4476,13 +4464,13 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B63" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C63" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D63" t="s">
         <v>9</v>
@@ -4502,13 +4490,13 @@
         <v>196</v>
       </c>
       <c r="C64" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D64" t="s">
         <v>9</v>
       </c>
       <c r="E64" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F64" s="1">
         <v>46245</v>
@@ -4516,13 +4504,13 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B65" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C65" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D65" t="s">
         <v>9</v>
@@ -4619,7 +4607,7 @@
         <v>217</v>
       </c>
       <c r="B70" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C70" t="s">
         <v>215</v>
@@ -4699,16 +4687,16 @@
         <v>230</v>
       </c>
       <c r="B74" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" t="s">
         <v>231</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" t="s">
         <v>232</v>
-      </c>
-      <c r="D74" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" t="s">
-        <v>233</v>
       </c>
       <c r="F74" s="1">
         <v>46245</v>
@@ -4716,10 +4704,10 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
+        <v>233</v>
+      </c>
+      <c r="B75" t="s">
         <v>234</v>
-      </c>
-      <c r="B75" t="s">
-        <v>149</v>
       </c>
       <c r="C75" t="s">
         <v>235</v>
@@ -4742,13 +4730,13 @@
         <v>238</v>
       </c>
       <c r="C76" t="s">
+        <v>235</v>
+      </c>
+      <c r="D76" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" t="s">
         <v>239</v>
-      </c>
-      <c r="D76" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" t="s">
-        <v>240</v>
       </c>
       <c r="F76" s="1">
         <v>46245</v>
@@ -4756,19 +4744,19 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
+        <v>240</v>
+      </c>
+      <c r="B77" t="s">
+        <v>42</v>
+      </c>
+      <c r="C77" t="s">
+        <v>235</v>
+      </c>
+      <c r="D77" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" t="s">
         <v>241</v>
-      </c>
-      <c r="B77" t="s">
-        <v>242</v>
-      </c>
-      <c r="C77" t="s">
-        <v>239</v>
-      </c>
-      <c r="D77" t="s">
-        <v>9</v>
-      </c>
-      <c r="E77" t="s">
-        <v>243</v>
       </c>
       <c r="F77" s="1">
         <v>46245</v>
@@ -4776,19 +4764,19 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
+        <v>242</v>
+      </c>
+      <c r="B78" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" t="s">
+        <v>243</v>
+      </c>
+      <c r="D78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" t="s">
         <v>244</v>
-      </c>
-      <c r="B78" t="s">
-        <v>38</v>
-      </c>
-      <c r="C78" t="s">
-        <v>239</v>
-      </c>
-      <c r="D78" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" t="s">
-        <v>245</v>
       </c>
       <c r="F78" s="1">
         <v>46245</v>
@@ -4796,19 +4784,19 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
+        <v>245</v>
+      </c>
+      <c r="B79" t="s">
+        <v>25</v>
+      </c>
+      <c r="C79" t="s">
+        <v>243</v>
+      </c>
+      <c r="D79" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" t="s">
         <v>246</v>
-      </c>
-      <c r="B79" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" t="s">
-        <v>247</v>
-      </c>
-      <c r="D79" t="s">
-        <v>9</v>
-      </c>
-      <c r="E79" t="s">
-        <v>248</v>
       </c>
       <c r="F79" s="1">
         <v>46245</v>
@@ -4816,13 +4804,13 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
+        <v>247</v>
+      </c>
+      <c r="B80" t="s">
+        <v>248</v>
+      </c>
+      <c r="C80" t="s">
         <v>249</v>
-      </c>
-      <c r="B80" t="s">
-        <v>21</v>
-      </c>
-      <c r="C80" t="s">
-        <v>247</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
@@ -4839,16 +4827,16 @@
         <v>251</v>
       </c>
       <c r="B81" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" t="s">
         <v>252</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" t="s">
         <v>253</v>
-      </c>
-      <c r="D81" t="s">
-        <v>9</v>
-      </c>
-      <c r="E81" t="s">
-        <v>254</v>
       </c>
       <c r="F81" s="1">
         <v>46245</v>
@@ -4856,13 +4844,13 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
+        <v>254</v>
+      </c>
+      <c r="B82" t="s">
         <v>255</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>256</v>
-      </c>
-      <c r="C82" t="s">
-        <v>253</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
@@ -4879,7 +4867,7 @@
         <v>258</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C83" t="s">
         <v>259</v>
@@ -4899,16 +4887,16 @@
         <v>261</v>
       </c>
       <c r="B84" t="s">
+        <v>207</v>
+      </c>
+      <c r="C84" t="s">
         <v>262</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" t="s">
         <v>263</v>
-      </c>
-      <c r="D84" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" t="s">
-        <v>264</v>
       </c>
       <c r="F84" s="1">
         <v>46245</v>
@@ -4916,19 +4904,19 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
+        <v>264</v>
+      </c>
+      <c r="B85" t="s">
+        <v>224</v>
+      </c>
+      <c r="C85" t="s">
         <v>265</v>
       </c>
-      <c r="B85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" t="s">
         <v>266</v>
-      </c>
-      <c r="D85" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" t="s">
-        <v>267</v>
       </c>
       <c r="F85" s="1">
         <v>46245</v>
@@ -4936,19 +4924,19 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
+        <v>267</v>
+      </c>
+      <c r="B86" t="s">
+        <v>214</v>
+      </c>
+      <c r="C86" t="s">
+        <v>265</v>
+      </c>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" t="s">
         <v>268</v>
-      </c>
-      <c r="B86" t="s">
-        <v>207</v>
-      </c>
-      <c r="C86" t="s">
-        <v>269</v>
-      </c>
-      <c r="D86" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" t="s">
-        <v>270</v>
       </c>
       <c r="F86" s="1">
         <v>46245</v>
@@ -4956,19 +4944,19 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
+        <v>269</v>
+      </c>
+      <c r="B87" t="s">
+        <v>270</v>
+      </c>
+      <c r="C87" t="s">
+        <v>265</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" t="s">
         <v>271</v>
-      </c>
-      <c r="B87" t="s">
-        <v>224</v>
-      </c>
-      <c r="C87" t="s">
-        <v>272</v>
-      </c>
-      <c r="D87" t="s">
-        <v>9</v>
-      </c>
-      <c r="E87" t="s">
-        <v>273</v>
       </c>
       <c r="F87" s="1">
         <v>46245</v>
@@ -4976,13 +4964,13 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
+        <v>272</v>
+      </c>
+      <c r="B88" t="s">
+        <v>273</v>
+      </c>
+      <c r="C88" t="s">
         <v>274</v>
-      </c>
-      <c r="B88" t="s">
-        <v>214</v>
-      </c>
-      <c r="C88" t="s">
-        <v>272</v>
       </c>
       <c r="D88" t="s">
         <v>9</v>
@@ -4999,10 +4987,10 @@
         <v>276</v>
       </c>
       <c r="B89" t="s">
+        <v>111</v>
+      </c>
+      <c r="C89" t="s">
         <v>277</v>
-      </c>
-      <c r="C89" t="s">
-        <v>272</v>
       </c>
       <c r="D89" t="s">
         <v>9</v>
@@ -5019,16 +5007,16 @@
         <v>279</v>
       </c>
       <c r="B90" t="s">
+        <v>111</v>
+      </c>
+      <c r="C90" t="s">
+        <v>277</v>
+      </c>
+      <c r="D90" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" t="s">
         <v>280</v>
-      </c>
-      <c r="C90" t="s">
-        <v>281</v>
-      </c>
-      <c r="D90" t="s">
-        <v>9</v>
-      </c>
-      <c r="E90" t="s">
-        <v>282</v>
       </c>
       <c r="F90" s="1">
         <v>46245</v>
@@ -5036,19 +5024,19 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
+        <v>281</v>
+      </c>
+      <c r="B91" t="s">
+        <v>114</v>
+      </c>
+      <c r="C91" t="s">
+        <v>282</v>
+      </c>
+      <c r="D91" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" t="s">
         <v>283</v>
-      </c>
-      <c r="B91" t="s">
-        <v>107</v>
-      </c>
-      <c r="C91" t="s">
-        <v>284</v>
-      </c>
-      <c r="D91" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" t="s">
-        <v>285</v>
       </c>
       <c r="F91" s="1">
         <v>46245</v>
@@ -5056,13 +5044,13 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
+        <v>284</v>
+      </c>
+      <c r="B92" t="s">
+        <v>285</v>
+      </c>
+      <c r="C92" t="s">
         <v>286</v>
-      </c>
-      <c r="B92" t="s">
-        <v>107</v>
-      </c>
-      <c r="C92" t="s">
-        <v>284</v>
       </c>
       <c r="D92" t="s">
         <v>9</v>
@@ -5079,7 +5067,7 @@
         <v>288</v>
       </c>
       <c r="B93" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="C93" t="s">
         <v>289</v>
@@ -5119,16 +5107,16 @@
         <v>295</v>
       </c>
       <c r="B95" t="s">
-        <v>184</v>
+        <v>296</v>
       </c>
       <c r="C95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D95" t="s">
         <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F95" s="1">
         <v>46245</v>
@@ -5136,19 +5124,19 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B96" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C96" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D96" t="s">
         <v>9</v>
       </c>
       <c r="E96" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F96" s="1">
         <v>46245</v>
@@ -5156,19 +5144,19 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B97" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C97" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F97" s="1">
         <v>46245</v>
@@ -5176,19 +5164,19 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B98" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C98" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D98" t="s">
         <v>9</v>
       </c>
       <c r="E98" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F98" s="1">
         <v>46245</v>
@@ -5196,19 +5184,19 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B99" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C99" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
       </c>
       <c r="E99" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F99" s="1">
         <v>46245</v>
@@ -5216,13 +5204,13 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B100" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C100" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D100" t="s">
         <v>9</v>
@@ -5239,16 +5227,16 @@
         <v>318</v>
       </c>
       <c r="B101" t="s">
+        <v>32</v>
+      </c>
+      <c r="C101" t="s">
         <v>319</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" t="s">
         <v>320</v>
-      </c>
-      <c r="D101" t="s">
-        <v>9</v>
-      </c>
-      <c r="E101" t="s">
-        <v>321</v>
       </c>
       <c r="F101" s="1">
         <v>46245</v>
@@ -5256,19 +5244,19 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
+        <v>321</v>
+      </c>
+      <c r="B102" t="s">
+        <v>196</v>
+      </c>
+      <c r="C102" t="s">
         <v>322</v>
       </c>
-      <c r="B102" t="s">
+      <c r="D102" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" t="s">
         <v>323</v>
-      </c>
-      <c r="C102" t="s">
-        <v>320</v>
-      </c>
-      <c r="D102" t="s">
-        <v>9</v>
-      </c>
-      <c r="E102" t="s">
-        <v>324</v>
       </c>
       <c r="F102" s="1">
         <v>46245</v>
@@ -5276,19 +5264,19 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
+        <v>324</v>
+      </c>
+      <c r="B103" t="s">
+        <v>196</v>
+      </c>
+      <c r="C103" t="s">
+        <v>322</v>
+      </c>
+      <c r="D103" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" t="s">
         <v>325</v>
-      </c>
-      <c r="B103" t="s">
-        <v>28</v>
-      </c>
-      <c r="C103" t="s">
-        <v>326</v>
-      </c>
-      <c r="D103" t="s">
-        <v>9</v>
-      </c>
-      <c r="E103" t="s">
-        <v>327</v>
       </c>
       <c r="F103" s="1">
         <v>46245</v>
@@ -5296,19 +5284,19 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
+        <v>326</v>
+      </c>
+      <c r="B104" t="s">
+        <v>70</v>
+      </c>
+      <c r="C104" t="s">
+        <v>327</v>
+      </c>
+      <c r="D104" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" t="s">
         <v>328</v>
-      </c>
-      <c r="B104" t="s">
-        <v>192</v>
-      </c>
-      <c r="C104" t="s">
-        <v>329</v>
-      </c>
-      <c r="D104" t="s">
-        <v>9</v>
-      </c>
-      <c r="E104" t="s">
-        <v>330</v>
       </c>
       <c r="F104" s="1">
         <v>46245</v>
@@ -5316,13 +5304,13 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
+        <v>329</v>
+      </c>
+      <c r="B105" t="s">
+        <v>330</v>
+      </c>
+      <c r="C105" t="s">
         <v>331</v>
-      </c>
-      <c r="B105" t="s">
-        <v>192</v>
-      </c>
-      <c r="C105" t="s">
-        <v>329</v>
       </c>
       <c r="D105" t="s">
         <v>9</v>
@@ -5339,7 +5327,7 @@
         <v>333</v>
       </c>
       <c r="B106" t="s">
-        <v>66</v>
+        <v>248</v>
       </c>
       <c r="C106" t="s">
         <v>334</v>
@@ -5359,16 +5347,16 @@
         <v>336</v>
       </c>
       <c r="B107" t="s">
+        <v>107</v>
+      </c>
+      <c r="C107" t="s">
         <v>337</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" t="s">
         <v>338</v>
-      </c>
-      <c r="D107" t="s">
-        <v>9</v>
-      </c>
-      <c r="E107" t="s">
-        <v>339</v>
       </c>
       <c r="F107" s="1">
         <v>46245</v>
@@ -5376,19 +5364,19 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
+        <v>339</v>
+      </c>
+      <c r="B108" t="s">
+        <v>107</v>
+      </c>
+      <c r="C108" t="s">
+        <v>337</v>
+      </c>
+      <c r="D108" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" t="s">
         <v>340</v>
-      </c>
-      <c r="B108" t="s">
-        <v>256</v>
-      </c>
-      <c r="C108" t="s">
-        <v>341</v>
-      </c>
-      <c r="D108" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" t="s">
-        <v>342</v>
       </c>
       <c r="F108" s="1">
         <v>46245</v>
@@ -5396,19 +5384,19 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B109" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D109" t="s">
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F109" s="1">
         <v>46245</v>
@@ -5416,19 +5404,19 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C110" t="s">
+        <v>337</v>
+      </c>
+      <c r="D110" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" t="s">
         <v>344</v>
-      </c>
-      <c r="D110" t="s">
-        <v>9</v>
-      </c>
-      <c r="E110" t="s">
-        <v>347</v>
       </c>
       <c r="F110" s="1">
         <v>46245</v>
@@ -5436,19 +5424,19 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s">
-        <v>103</v>
+        <v>292</v>
       </c>
       <c r="C111" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D111" t="s">
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F111" s="1">
         <v>46245</v>
@@ -5456,19 +5444,19 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
+        <v>348</v>
+      </c>
+      <c r="B112" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" t="s">
+        <v>349</v>
+      </c>
+      <c r="D112" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" t="s">
         <v>350</v>
-      </c>
-      <c r="B112" t="s">
-        <v>103</v>
-      </c>
-      <c r="C112" t="s">
-        <v>344</v>
-      </c>
-      <c r="D112" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" t="s">
-        <v>351</v>
       </c>
       <c r="F112" s="1">
         <v>46245</v>
@@ -5476,19 +5464,19 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
+        <v>351</v>
+      </c>
+      <c r="B113" t="s">
+        <v>107</v>
+      </c>
+      <c r="C113" t="s">
         <v>352</v>
       </c>
-      <c r="B113" t="s">
-        <v>299</v>
-      </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" t="s">
         <v>353</v>
-      </c>
-      <c r="D113" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" t="s">
-        <v>354</v>
       </c>
       <c r="F113" s="1">
         <v>46245</v>
@@ -5496,19 +5484,19 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
+        <v>354</v>
+      </c>
+      <c r="B114" t="s">
+        <v>70</v>
+      </c>
+      <c r="C114" t="s">
         <v>355</v>
       </c>
-      <c r="B114" t="s">
-        <v>15</v>
-      </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" t="s">
         <v>356</v>
-      </c>
-      <c r="D114" t="s">
-        <v>9</v>
-      </c>
-      <c r="E114" t="s">
-        <v>357</v>
       </c>
       <c r="F114" s="1">
         <v>46245</v>
@@ -5516,19 +5504,19 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
+        <v>357</v>
+      </c>
+      <c r="B115" t="s">
+        <v>292</v>
+      </c>
+      <c r="C115" t="s">
         <v>358</v>
       </c>
-      <c r="B115" t="s">
-        <v>103</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" t="s">
         <v>359</v>
-      </c>
-      <c r="D115" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" t="s">
-        <v>360</v>
       </c>
       <c r="F115" s="1">
         <v>46245</v>
@@ -5536,19 +5524,19 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
+        <v>360</v>
+      </c>
+      <c r="B116" t="s">
+        <v>292</v>
+      </c>
+      <c r="C116" t="s">
+        <v>358</v>
+      </c>
+      <c r="D116" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" t="s">
         <v>361</v>
-      </c>
-      <c r="B116" t="s">
-        <v>66</v>
-      </c>
-      <c r="C116" t="s">
-        <v>362</v>
-      </c>
-      <c r="D116" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" t="s">
-        <v>363</v>
       </c>
       <c r="F116" s="1">
         <v>46245</v>
@@ -5556,19 +5544,19 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B117" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C117" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="D117" t="s">
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F117" s="1">
         <v>46245</v>
@@ -5576,19 +5564,19 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
+        <v>364</v>
+      </c>
+      <c r="B118" t="s">
+        <v>365</v>
+      </c>
+      <c r="C118" t="s">
+        <v>366</v>
+      </c>
+      <c r="D118" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" t="s">
         <v>367</v>
-      </c>
-      <c r="B118" t="s">
-        <v>299</v>
-      </c>
-      <c r="C118" t="s">
-        <v>365</v>
-      </c>
-      <c r="D118" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" t="s">
-        <v>368</v>
       </c>
       <c r="F118" s="1">
         <v>46245</v>
@@ -5596,19 +5584,19 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
+        <v>368</v>
+      </c>
+      <c r="B119" t="s">
+        <v>255</v>
+      </c>
+      <c r="C119" t="s">
+        <v>366</v>
+      </c>
+      <c r="D119" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" t="s">
         <v>369</v>
-      </c>
-      <c r="B119" t="s">
-        <v>299</v>
-      </c>
-      <c r="C119" t="s">
-        <v>365</v>
-      </c>
-      <c r="D119" t="s">
-        <v>9</v>
-      </c>
-      <c r="E119" t="s">
-        <v>370</v>
       </c>
       <c r="F119" s="1">
         <v>46245</v>
@@ -5616,19 +5604,19 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
+        <v>370</v>
+      </c>
+      <c r="B120" t="s">
+        <v>255</v>
+      </c>
+      <c r="C120" t="s">
         <v>371</v>
       </c>
-      <c r="B120" t="s">
+      <c r="D120" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" t="s">
         <v>372</v>
-      </c>
-      <c r="C120" t="s">
-        <v>373</v>
-      </c>
-      <c r="D120" t="s">
-        <v>9</v>
-      </c>
-      <c r="E120" t="s">
-        <v>374</v>
       </c>
       <c r="F120" s="1">
         <v>46245</v>
@@ -5636,19 +5624,19 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
+        <v>373</v>
+      </c>
+      <c r="B121" t="s">
+        <v>374</v>
+      </c>
+      <c r="C121" t="s">
+        <v>371</v>
+      </c>
+      <c r="D121" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" t="s">
         <v>375</v>
-      </c>
-      <c r="B121" t="s">
-        <v>262</v>
-      </c>
-      <c r="C121" t="s">
-        <v>373</v>
-      </c>
-      <c r="D121" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" t="s">
-        <v>376</v>
       </c>
       <c r="F121" s="1">
         <v>46245</v>
@@ -5656,19 +5644,19 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
+        <v>376</v>
+      </c>
+      <c r="B122" t="s">
         <v>377</v>
       </c>
-      <c r="B122" t="s">
-        <v>262</v>
-      </c>
       <c r="C122" t="s">
+        <v>371</v>
+      </c>
+      <c r="D122" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" t="s">
         <v>378</v>
-      </c>
-      <c r="D122" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" t="s">
-        <v>379</v>
       </c>
       <c r="F122" s="1">
         <v>46245</v>
@@ -5676,19 +5664,19 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
+        <v>379</v>
+      </c>
+      <c r="B123" t="s">
+        <v>273</v>
+      </c>
+      <c r="C123" t="s">
+        <v>371</v>
+      </c>
+      <c r="D123" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" t="s">
         <v>380</v>
-      </c>
-      <c r="B123" t="s">
-        <v>381</v>
-      </c>
-      <c r="C123" t="s">
-        <v>378</v>
-      </c>
-      <c r="D123" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" t="s">
-        <v>382</v>
       </c>
       <c r="F123" s="1">
         <v>46245</v>
@@ -5696,19 +5684,19 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
+        <v>381</v>
+      </c>
+      <c r="B124" t="s">
+        <v>382</v>
+      </c>
+      <c r="C124" t="s">
+        <v>371</v>
+      </c>
+      <c r="D124" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" t="s">
         <v>383</v>
-      </c>
-      <c r="B124" t="s">
-        <v>384</v>
-      </c>
-      <c r="C124" t="s">
-        <v>378</v>
-      </c>
-      <c r="D124" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" t="s">
-        <v>385</v>
       </c>
       <c r="F124" s="1">
         <v>46245</v>
@@ -5716,19 +5704,19 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B125" t="s">
-        <v>280</v>
+        <v>382</v>
       </c>
       <c r="C125" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F125" s="1">
         <v>46245</v>
@@ -5736,19 +5724,19 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B126" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C126" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D126" t="s">
         <v>9</v>
       </c>
       <c r="E126" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F126" s="1">
         <v>46245</v>
@@ -5756,19 +5744,19 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B127" t="s">
+        <v>382</v>
+      </c>
+      <c r="C127" t="s">
+        <v>371</v>
+      </c>
+      <c r="D127" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" t="s">
         <v>389</v>
-      </c>
-      <c r="C127" t="s">
-        <v>378</v>
-      </c>
-      <c r="D127" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" t="s">
-        <v>392</v>
       </c>
       <c r="F127" s="1">
         <v>46245</v>
@@ -5776,19 +5764,19 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B128" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C128" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D128" t="s">
         <v>9</v>
       </c>
       <c r="E128" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F128" s="1">
         <v>46245</v>
@@ -5796,19 +5784,19 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B129" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C129" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D129" t="s">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F129" s="1">
         <v>46245</v>
@@ -5816,19 +5804,19 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B130" t="s">
-        <v>389</v>
+        <v>55</v>
       </c>
       <c r="C130" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D130" t="s">
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F130" s="1">
         <v>46245</v>
@@ -5836,19 +5824,19 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B131" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C131" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D131" t="s">
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F131" s="1">
         <v>46245</v>
@@ -5856,19 +5844,19 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
+        <v>399</v>
+      </c>
+      <c r="B132" t="s">
+        <v>400</v>
+      </c>
+      <c r="C132" t="s">
+        <v>371</v>
+      </c>
+      <c r="D132" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" t="s">
         <v>401</v>
-      </c>
-      <c r="B132" t="s">
-        <v>51</v>
-      </c>
-      <c r="C132" t="s">
-        <v>378</v>
-      </c>
-      <c r="D132" t="s">
-        <v>9</v>
-      </c>
-      <c r="E132" t="s">
-        <v>402</v>
       </c>
       <c r="F132" s="1">
         <v>46245</v>
@@ -5876,19 +5864,19 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
+        <v>402</v>
+      </c>
+      <c r="B133" t="s">
         <v>403</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
+        <v>371</v>
+      </c>
+      <c r="D133" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" t="s">
         <v>404</v>
-      </c>
-      <c r="C133" t="s">
-        <v>378</v>
-      </c>
-      <c r="D133" t="s">
-        <v>9</v>
-      </c>
-      <c r="E133" t="s">
-        <v>405</v>
       </c>
       <c r="F133" s="1">
         <v>46245</v>
@@ -5896,19 +5884,19 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
+        <v>405</v>
+      </c>
+      <c r="B134" t="s">
+        <v>403</v>
+      </c>
+      <c r="C134" t="s">
+        <v>371</v>
+      </c>
+      <c r="D134" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" t="s">
         <v>406</v>
-      </c>
-      <c r="B134" t="s">
-        <v>407</v>
-      </c>
-      <c r="C134" t="s">
-        <v>378</v>
-      </c>
-      <c r="D134" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" t="s">
-        <v>408</v>
       </c>
       <c r="F134" s="1">
         <v>46245</v>
@@ -5916,19 +5904,19 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B135" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="C135" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D135" t="s">
         <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F135" s="1">
         <v>46245</v>
@@ -5936,19 +5924,19 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B136" t="s">
         <v>410</v>
       </c>
       <c r="C136" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D136" t="s">
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F136" s="1">
         <v>46245</v>
@@ -5956,19 +5944,19 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
+        <v>412</v>
+      </c>
+      <c r="B137" t="s">
+        <v>413</v>
+      </c>
+      <c r="C137" t="s">
+        <v>371</v>
+      </c>
+      <c r="D137" t="s">
+        <v>9</v>
+      </c>
+      <c r="E137" t="s">
         <v>414</v>
-      </c>
-      <c r="B137" t="s">
-        <v>410</v>
-      </c>
-      <c r="C137" t="s">
-        <v>378</v>
-      </c>
-      <c r="D137" t="s">
-        <v>9</v>
-      </c>
-      <c r="E137" t="s">
-        <v>415</v>
       </c>
       <c r="F137" s="1">
         <v>46245</v>
@@ -5976,19 +5964,19 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
+        <v>415</v>
+      </c>
+      <c r="B138" t="s">
         <v>416</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" t="s">
+        <v>371</v>
+      </c>
+      <c r="D138" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" t="s">
         <v>417</v>
-      </c>
-      <c r="C138" t="s">
-        <v>378</v>
-      </c>
-      <c r="D138" t="s">
-        <v>9</v>
-      </c>
-      <c r="E138" t="s">
-        <v>418</v>
       </c>
       <c r="F138" s="1">
         <v>46245</v>
@@ -5996,19 +5984,19 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
+        <v>418</v>
+      </c>
+      <c r="B139" t="s">
         <v>419</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" t="s">
+        <v>371</v>
+      </c>
+      <c r="D139" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" t="s">
         <v>420</v>
-      </c>
-      <c r="C139" t="s">
-        <v>378</v>
-      </c>
-      <c r="D139" t="s">
-        <v>9</v>
-      </c>
-      <c r="E139" t="s">
-        <v>421</v>
       </c>
       <c r="F139" s="1">
         <v>46245</v>
@@ -6016,19 +6004,19 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
+        <v>421</v>
+      </c>
+      <c r="B140" t="s">
         <v>422</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" t="s">
+        <v>371</v>
+      </c>
+      <c r="D140" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" t="s">
         <v>423</v>
-      </c>
-      <c r="C140" t="s">
-        <v>378</v>
-      </c>
-      <c r="D140" t="s">
-        <v>9</v>
-      </c>
-      <c r="E140" t="s">
-        <v>424</v>
       </c>
       <c r="F140" s="1">
         <v>46245</v>
@@ -6036,19 +6024,19 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
+        <v>424</v>
+      </c>
+      <c r="B141" t="s">
         <v>425</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
+        <v>371</v>
+      </c>
+      <c r="D141" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" t="s">
         <v>426</v>
-      </c>
-      <c r="C141" t="s">
-        <v>378</v>
-      </c>
-      <c r="D141" t="s">
-        <v>9</v>
-      </c>
-      <c r="E141" t="s">
-        <v>427</v>
       </c>
       <c r="F141" s="1">
         <v>46245</v>
@@ -6056,19 +6044,19 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
+        <v>427</v>
+      </c>
+      <c r="B142" t="s">
         <v>428</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
+        <v>371</v>
+      </c>
+      <c r="D142" t="s">
+        <v>9</v>
+      </c>
+      <c r="E142" t="s">
         <v>429</v>
-      </c>
-      <c r="C142" t="s">
-        <v>378</v>
-      </c>
-      <c r="D142" t="s">
-        <v>9</v>
-      </c>
-      <c r="E142" t="s">
-        <v>430</v>
       </c>
       <c r="F142" s="1">
         <v>46245</v>
@@ -6076,19 +6064,19 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
+        <v>430</v>
+      </c>
+      <c r="B143" t="s">
+        <v>25</v>
+      </c>
+      <c r="C143" t="s">
+        <v>371</v>
+      </c>
+      <c r="D143" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143" t="s">
         <v>431</v>
-      </c>
-      <c r="B143" t="s">
-        <v>432</v>
-      </c>
-      <c r="C143" t="s">
-        <v>378</v>
-      </c>
-      <c r="D143" t="s">
-        <v>9</v>
-      </c>
-      <c r="E143" t="s">
-        <v>433</v>
       </c>
       <c r="F143" s="1">
         <v>46245</v>
@@ -6096,19 +6084,19 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
+        <v>432</v>
+      </c>
+      <c r="B144" t="s">
+        <v>433</v>
+      </c>
+      <c r="C144" t="s">
+        <v>371</v>
+      </c>
+      <c r="D144" t="s">
+        <v>9</v>
+      </c>
+      <c r="E144" t="s">
         <v>434</v>
-      </c>
-      <c r="B144" t="s">
-        <v>435</v>
-      </c>
-      <c r="C144" t="s">
-        <v>378</v>
-      </c>
-      <c r="D144" t="s">
-        <v>9</v>
-      </c>
-      <c r="E144" t="s">
-        <v>436</v>
       </c>
       <c r="F144" s="1">
         <v>46245</v>
@@ -6116,19 +6104,19 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B145" t="s">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="C145" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D145" t="s">
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F145" s="1">
         <v>46245</v>
@@ -6136,19 +6124,19 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
+        <v>437</v>
+      </c>
+      <c r="B146" t="s">
+        <v>438</v>
+      </c>
+      <c r="C146" t="s">
+        <v>371</v>
+      </c>
+      <c r="D146" t="s">
+        <v>9</v>
+      </c>
+      <c r="E146" t="s">
         <v>439</v>
-      </c>
-      <c r="B146" t="s">
-        <v>440</v>
-      </c>
-      <c r="C146" t="s">
-        <v>378</v>
-      </c>
-      <c r="D146" t="s">
-        <v>9</v>
-      </c>
-      <c r="E146" t="s">
-        <v>441</v>
       </c>
       <c r="F146" s="1">
         <v>46245</v>
@@ -6156,19 +6144,19 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B147" t="s">
-        <v>323</v>
+        <v>107</v>
       </c>
       <c r="C147" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D147" t="s">
         <v>9</v>
       </c>
       <c r="E147" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F147" s="1">
         <v>46245</v>
@@ -6176,19 +6164,19 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B148" t="s">
-        <v>445</v>
+        <v>107</v>
       </c>
       <c r="C148" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D148" t="s">
         <v>9</v>
       </c>
       <c r="E148" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F148" s="1">
         <v>46245</v>
@@ -6196,19 +6184,19 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B149" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C149" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D149" t="s">
         <v>9</v>
       </c>
       <c r="E149" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F149" s="1">
         <v>46245</v>
@@ -6216,19 +6204,19 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B150" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C150" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D150" t="s">
         <v>9</v>
       </c>
       <c r="E150" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F150" s="1">
         <v>46245</v>
@@ -6236,19 +6224,19 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B151" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C151" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D151" t="s">
         <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F151" s="1">
         <v>46245</v>
@@ -6256,19 +6244,19 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B152" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C152" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D152" t="s">
         <v>9</v>
       </c>
       <c r="E152" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F152" s="1">
         <v>46245</v>
@@ -6276,19 +6264,19 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B153" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C153" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D153" t="s">
         <v>9</v>
       </c>
       <c r="E153" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F153" s="1">
         <v>46245</v>
@@ -6296,19 +6284,19 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B154" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C154" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D154" t="s">
         <v>9</v>
       </c>
       <c r="E154" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F154" s="1">
         <v>46245</v>
@@ -6316,19 +6304,19 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B155" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C155" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D155" t="s">
         <v>9</v>
       </c>
       <c r="E155" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F155" s="1">
         <v>46245</v>
@@ -6336,19 +6324,19 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B156" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C156" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D156" t="s">
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F156" s="1">
         <v>46245</v>
@@ -6356,19 +6344,19 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B157" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C157" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D157" t="s">
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F157" s="1">
         <v>46245</v>
@@ -6376,19 +6364,19 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B158" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C158" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D158" t="s">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F158" s="1">
         <v>46245</v>
@@ -6396,19 +6384,19 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B159" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C159" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D159" t="s">
         <v>9</v>
       </c>
       <c r="E159" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F159" s="1">
         <v>46245</v>
@@ -6416,19 +6404,19 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B160" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C160" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D160" t="s">
         <v>9</v>
       </c>
       <c r="E160" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F160" s="1">
         <v>46245</v>
@@ -6436,19 +6424,19 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B161" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C161" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D161" t="s">
         <v>9</v>
       </c>
       <c r="E161" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F161" s="1">
         <v>46245</v>
@@ -6456,19 +6444,19 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B162" t="s">
-        <v>103</v>
+        <v>214</v>
       </c>
       <c r="C162" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D162" t="s">
         <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F162" s="1">
         <v>46245</v>
@@ -6476,19 +6464,19 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B163" t="s">
-        <v>103</v>
+        <v>292</v>
       </c>
       <c r="C163" t="s">
-        <v>378</v>
+        <v>473</v>
       </c>
       <c r="D163" t="s">
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F163" s="1">
         <v>46245</v>
@@ -6496,19 +6484,19 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B164" t="s">
-        <v>214</v>
+        <v>292</v>
       </c>
       <c r="C164" t="s">
-        <v>378</v>
+        <v>473</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F164" s="1">
         <v>46245</v>
@@ -6516,19 +6504,19 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B165" t="s">
-        <v>299</v>
+        <v>200</v>
       </c>
       <c r="C165" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F165" s="1">
         <v>46245</v>
@@ -6536,19 +6524,19 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B166" t="s">
-        <v>299</v>
+        <v>480</v>
       </c>
       <c r="C166" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D166" t="s">
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F166" s="1">
         <v>46245</v>
@@ -6556,19 +6544,19 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B167" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="C167" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D167" t="s">
         <v>9</v>
       </c>
       <c r="E167" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F167" s="1">
         <v>46245</v>
@@ -6576,19 +6564,19 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B168" t="s">
-        <v>487</v>
+        <v>18</v>
       </c>
       <c r="C168" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D168" t="s">
         <v>9</v>
       </c>
       <c r="E168" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F168" s="1">
         <v>46245</v>
@@ -6596,19 +6584,19 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B169" t="s">
-        <v>7</v>
+        <v>487</v>
       </c>
       <c r="C169" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D169" t="s">
         <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F169" s="1">
         <v>46245</v>
@@ -6616,19 +6604,19 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B170" t="s">
-        <v>7</v>
+        <v>480</v>
       </c>
       <c r="C170" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D170" t="s">
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F170" s="1">
         <v>46245</v>
@@ -6636,19 +6624,19 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B171" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="C171" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D171" t="s">
         <v>9</v>
       </c>
       <c r="E171" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F171" s="1">
         <v>46245</v>
@@ -6656,19 +6644,19 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B172" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="C172" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D172" t="s">
         <v>9</v>
       </c>
       <c r="E172" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F172" s="1">
         <v>46245</v>
@@ -6676,19 +6664,19 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
+        <v>496</v>
+      </c>
+      <c r="B173" t="s">
+        <v>497</v>
+      </c>
+      <c r="C173" t="s">
+        <v>473</v>
+      </c>
+      <c r="D173" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" t="s">
         <v>498</v>
-      </c>
-      <c r="B173" t="s">
-        <v>487</v>
-      </c>
-      <c r="C173" t="s">
-        <v>480</v>
-      </c>
-      <c r="D173" t="s">
-        <v>9</v>
-      </c>
-      <c r="E173" t="s">
-        <v>499</v>
       </c>
       <c r="F173" s="1">
         <v>46245</v>
@@ -6696,13 +6684,13 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
+        <v>499</v>
+      </c>
+      <c r="B174" t="s">
         <v>500</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C174" t="s">
         <v>501</v>
-      </c>
-      <c r="C174" t="s">
-        <v>480</v>
       </c>
       <c r="D174" t="s">
         <v>9</v>
@@ -6719,10 +6707,10 @@
         <v>503</v>
       </c>
       <c r="B175" t="s">
+        <v>330</v>
+      </c>
+      <c r="C175" t="s">
         <v>504</v>
-      </c>
-      <c r="C175" t="s">
-        <v>480</v>
       </c>
       <c r="D175" t="s">
         <v>9</v>
@@ -6759,16 +6747,16 @@
         <v>510</v>
       </c>
       <c r="B177" t="s">
-        <v>337</v>
+        <v>511</v>
       </c>
       <c r="C177" t="s">
-        <v>511</v>
+        <v>19</v>
       </c>
       <c r="D177" t="s">
-        <v>9</v>
+        <v>512</v>
       </c>
       <c r="E177" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F177" s="1">
         <v>46245</v>
@@ -6776,16 +6764,16 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B178" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C178" t="s">
-        <v>515</v>
+        <v>46</v>
       </c>
       <c r="D178" t="s">
-        <v>9</v>
+        <v>512</v>
       </c>
       <c r="E178" t="s">
         <v>516</v>
@@ -6802,13 +6790,13 @@
         <v>518</v>
       </c>
       <c r="C179" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="D179" t="s">
+        <v>512</v>
+      </c>
+      <c r="E179" t="s">
         <v>519</v>
-      </c>
-      <c r="E179" t="s">
-        <v>520</v>
       </c>
       <c r="F179" s="1">
         <v>46245</v>
@@ -6816,19 +6804,19 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
+        <v>520</v>
+      </c>
+      <c r="B180" t="s">
         <v>521</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
+        <v>73</v>
+      </c>
+      <c r="D180" t="s">
+        <v>512</v>
+      </c>
+      <c r="E180" t="s">
         <v>522</v>
-      </c>
-      <c r="C180" t="s">
-        <v>42</v>
-      </c>
-      <c r="D180" t="s">
-        <v>519</v>
-      </c>
-      <c r="E180" t="s">
-        <v>523</v>
       </c>
       <c r="F180" s="1">
         <v>46245</v>
@@ -6836,19 +6824,19 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
+        <v>523</v>
+      </c>
+      <c r="B181" t="s">
         <v>524</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
+        <v>221</v>
+      </c>
+      <c r="D181" t="s">
+        <v>512</v>
+      </c>
+      <c r="E181" t="s">
         <v>525</v>
-      </c>
-      <c r="C181" t="s">
-        <v>52</v>
-      </c>
-      <c r="D181" t="s">
-        <v>519</v>
-      </c>
-      <c r="E181" t="s">
-        <v>526</v>
       </c>
       <c r="F181" s="1">
         <v>46245</v>
@@ -6856,16 +6844,16 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
+        <v>526</v>
+      </c>
+      <c r="B182" t="s">
         <v>527</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
         <v>528</v>
       </c>
-      <c r="C182" t="s">
-        <v>69</v>
-      </c>
       <c r="D182" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E182" t="s">
         <v>529</v>
@@ -6882,13 +6870,13 @@
         <v>531</v>
       </c>
       <c r="C183" t="s">
-        <v>221</v>
+        <v>532</v>
       </c>
       <c r="D183" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E183" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F183" s="1">
         <v>46245</v>
@@ -6896,19 +6884,19 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B184" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C184" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D184" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E184" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F184" s="1">
         <v>46245</v>
@@ -6916,19 +6904,19 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B185" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C185" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D185" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E185" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F185" s="1">
         <v>46245</v>
@@ -6936,16 +6924,16 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B186" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="C186" t="s">
         <v>543</v>
       </c>
       <c r="D186" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E186" t="s">
         <v>544</v>
@@ -6962,10 +6950,10 @@
         <v>546</v>
       </c>
       <c r="C187" t="s">
+        <v>19</v>
+      </c>
+      <c r="D187" t="s">
         <v>547</v>
-      </c>
-      <c r="D187" t="s">
-        <v>519</v>
       </c>
       <c r="E187" t="s">
         <v>548</v>
@@ -6979,13 +6967,13 @@
         <v>549</v>
       </c>
       <c r="B188" t="s">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="C188" t="s">
-        <v>550</v>
+        <v>29</v>
       </c>
       <c r="D188" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="E188" t="s">
         <v>551</v>
@@ -7002,13 +6990,13 @@
         <v>553</v>
       </c>
       <c r="C189" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="D189" t="s">
+        <v>547</v>
+      </c>
+      <c r="E189" t="s">
         <v>554</v>
-      </c>
-      <c r="E189" t="s">
-        <v>555</v>
       </c>
       <c r="F189" s="1">
         <v>46245</v>
@@ -7016,19 +7004,19 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
+        <v>555</v>
+      </c>
+      <c r="B190" t="s">
         <v>556</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" t="s">
+        <v>231</v>
+      </c>
+      <c r="D190" t="s">
+        <v>547</v>
+      </c>
+      <c r="E190" t="s">
         <v>557</v>
-      </c>
-      <c r="C190" t="s">
-        <v>25</v>
-      </c>
-      <c r="D190" t="s">
-        <v>554</v>
-      </c>
-      <c r="E190" t="s">
-        <v>558</v>
       </c>
       <c r="F190" s="1">
         <v>46245</v>
@@ -7036,16 +7024,16 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
+        <v>558</v>
+      </c>
+      <c r="B191" t="s">
         <v>559</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
         <v>560</v>
       </c>
-      <c r="C191" t="s">
-        <v>114</v>
-      </c>
       <c r="D191" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E191" t="s">
         <v>561</v>
@@ -7059,13 +7047,13 @@
         <v>562</v>
       </c>
       <c r="B192" t="s">
+        <v>550</v>
+      </c>
+      <c r="C192" t="s">
         <v>563</v>
       </c>
-      <c r="C192" t="s">
-        <v>235</v>
-      </c>
       <c r="D192" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E192" t="s">
         <v>564</v>
@@ -7082,13 +7070,13 @@
         <v>566</v>
       </c>
       <c r="C193" t="s">
+        <v>563</v>
+      </c>
+      <c r="D193" t="s">
+        <v>547</v>
+      </c>
+      <c r="E193" t="s">
         <v>567</v>
-      </c>
-      <c r="D193" t="s">
-        <v>554</v>
-      </c>
-      <c r="E193" t="s">
-        <v>568</v>
       </c>
       <c r="F193" s="1">
         <v>46245</v>
@@ -7096,19 +7084,19 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
+        <v>568</v>
+      </c>
+      <c r="B194" t="s">
         <v>569</v>
       </c>
-      <c r="B194" t="s">
-        <v>557</v>
-      </c>
       <c r="C194" t="s">
+        <v>305</v>
+      </c>
+      <c r="D194" t="s">
+        <v>547</v>
+      </c>
+      <c r="E194" t="s">
         <v>570</v>
-      </c>
-      <c r="D194" t="s">
-        <v>554</v>
-      </c>
-      <c r="E194" t="s">
-        <v>571</v>
       </c>
       <c r="F194" s="1">
         <v>46245</v>
@@ -7116,16 +7104,16 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
+        <v>571</v>
+      </c>
+      <c r="B195" t="s">
         <v>572</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" t="s">
         <v>573</v>
       </c>
-      <c r="C195" t="s">
-        <v>570</v>
-      </c>
       <c r="D195" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E195" t="s">
         <v>574</v>
@@ -7139,13 +7127,13 @@
         <v>575</v>
       </c>
       <c r="B196" t="s">
+        <v>550</v>
+      </c>
+      <c r="C196" t="s">
         <v>576</v>
       </c>
-      <c r="C196" t="s">
-        <v>312</v>
-      </c>
       <c r="D196" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E196" t="s">
         <v>577</v>
@@ -7162,13 +7150,13 @@
         <v>579</v>
       </c>
       <c r="C197" t="s">
+        <v>576</v>
+      </c>
+      <c r="D197" t="s">
+        <v>547</v>
+      </c>
+      <c r="E197" t="s">
         <v>580</v>
-      </c>
-      <c r="D197" t="s">
-        <v>554</v>
-      </c>
-      <c r="E197" t="s">
-        <v>581</v>
       </c>
       <c r="F197" s="1">
         <v>46245</v>
@@ -7176,16 +7164,16 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
+        <v>581</v>
+      </c>
+      <c r="B198" t="s">
         <v>582</v>
       </c>
-      <c r="B198" t="s">
-        <v>557</v>
-      </c>
       <c r="C198" t="s">
+        <v>8</v>
+      </c>
+      <c r="D198" t="s">
         <v>583</v>
-      </c>
-      <c r="D198" t="s">
-        <v>554</v>
       </c>
       <c r="E198" t="s">
         <v>584</v>
@@ -7202,10 +7190,10 @@
         <v>586</v>
       </c>
       <c r="C199" t="s">
+        <v>36</v>
+      </c>
+      <c r="D199" t="s">
         <v>583</v>
-      </c>
-      <c r="D199" t="s">
-        <v>554</v>
       </c>
       <c r="E199" t="s">
         <v>587</v>
@@ -7222,13 +7210,13 @@
         <v>589</v>
       </c>
       <c r="C200" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D200" t="s">
+        <v>583</v>
+      </c>
+      <c r="E200" t="s">
         <v>590</v>
-      </c>
-      <c r="E200" t="s">
-        <v>591</v>
       </c>
       <c r="F200" s="1">
         <v>46245</v>
@@ -7236,19 +7224,19 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
+        <v>591</v>
+      </c>
+      <c r="B201" t="s">
         <v>592</v>
       </c>
-      <c r="B201" t="s">
+      <c r="C201" t="s">
+        <v>73</v>
+      </c>
+      <c r="D201" t="s">
+        <v>583</v>
+      </c>
+      <c r="E201" t="s">
         <v>593</v>
-      </c>
-      <c r="C201" t="s">
-        <v>42</v>
-      </c>
-      <c r="D201" t="s">
-        <v>590</v>
-      </c>
-      <c r="E201" t="s">
-        <v>594</v>
       </c>
       <c r="F201" s="1">
         <v>46245</v>
@@ -7256,16 +7244,16 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
+        <v>594</v>
+      </c>
+      <c r="B202" t="s">
         <v>595</v>
       </c>
-      <c r="B202" t="s">
+      <c r="C202" t="s">
         <v>596</v>
       </c>
-      <c r="C202" t="s">
-        <v>52</v>
-      </c>
       <c r="D202" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="E202" t="s">
         <v>597</v>
@@ -7282,10 +7270,10 @@
         <v>599</v>
       </c>
       <c r="C203" t="s">
-        <v>69</v>
+        <v>256</v>
       </c>
       <c r="D203" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="E203" t="s">
         <v>600</v>
@@ -7299,16 +7287,16 @@
         <v>601</v>
       </c>
       <c r="B204" t="s">
+        <v>589</v>
+      </c>
+      <c r="C204" t="s">
         <v>602</v>
       </c>
-      <c r="C204" t="s">
+      <c r="D204" t="s">
+        <v>583</v>
+      </c>
+      <c r="E204" t="s">
         <v>603</v>
-      </c>
-      <c r="D204" t="s">
-        <v>590</v>
-      </c>
-      <c r="E204" t="s">
-        <v>604</v>
       </c>
       <c r="F204" s="1">
         <v>46245</v>
@@ -7316,19 +7304,19 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
+        <v>604</v>
+      </c>
+      <c r="B205" t="s">
+        <v>595</v>
+      </c>
+      <c r="C205" t="s">
         <v>605</v>
       </c>
-      <c r="B205" t="s">
+      <c r="D205" t="s">
+        <v>583</v>
+      </c>
+      <c r="E205" t="s">
         <v>606</v>
-      </c>
-      <c r="C205" t="s">
-        <v>263</v>
-      </c>
-      <c r="D205" t="s">
-        <v>590</v>
-      </c>
-      <c r="E205" t="s">
-        <v>607</v>
       </c>
       <c r="F205" s="1">
         <v>46245</v>
@@ -7336,19 +7324,19 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
+        <v>607</v>
+      </c>
+      <c r="B206" t="s">
+        <v>550</v>
+      </c>
+      <c r="C206" t="s">
         <v>608</v>
       </c>
-      <c r="B206" t="s">
-        <v>596</v>
-      </c>
-      <c r="C206" t="s">
+      <c r="D206" t="s">
+        <v>583</v>
+      </c>
+      <c r="E206" t="s">
         <v>609</v>
-      </c>
-      <c r="D206" t="s">
-        <v>590</v>
-      </c>
-      <c r="E206" t="s">
-        <v>610</v>
       </c>
       <c r="F206" s="1">
         <v>46245</v>
@@ -7356,16 +7344,13 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
+        <v>610</v>
+      </c>
+      <c r="B207" t="s">
         <v>611</v>
       </c>
-      <c r="B207" t="s">
-        <v>602</v>
-      </c>
-      <c r="C207" t="s">
+      <c r="D207" t="s">
         <v>612</v>
-      </c>
-      <c r="D207" t="s">
-        <v>590</v>
       </c>
       <c r="E207" t="s">
         <v>613</v>
@@ -7379,16 +7364,13 @@
         <v>614</v>
       </c>
       <c r="B208" t="s">
-        <v>557</v>
-      </c>
-      <c r="C208" t="s">
+        <v>611</v>
+      </c>
+      <c r="D208" t="s">
+        <v>612</v>
+      </c>
+      <c r="E208" t="s">
         <v>615</v>
-      </c>
-      <c r="D208" t="s">
-        <v>590</v>
-      </c>
-      <c r="E208" t="s">
-        <v>616</v>
       </c>
       <c r="F208" s="1">
         <v>46245</v>
@@ -7396,16 +7378,16 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
+        <v>616</v>
+      </c>
+      <c r="B209" t="s">
+        <v>52</v>
+      </c>
+      <c r="D209" t="s">
+        <v>612</v>
+      </c>
+      <c r="E209" t="s">
         <v>617</v>
-      </c>
-      <c r="B209" t="s">
-        <v>618</v>
-      </c>
-      <c r="D209" t="s">
-        <v>619</v>
-      </c>
-      <c r="E209" t="s">
-        <v>620</v>
       </c>
       <c r="F209" s="1">
         <v>46245</v>
@@ -7413,16 +7395,16 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B210" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D210" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="E210" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="F210" s="1">
         <v>46245</v>
@@ -7430,16 +7412,16 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
+        <v>621</v>
+      </c>
+      <c r="B211" t="s">
+        <v>622</v>
+      </c>
+      <c r="D211" t="s">
+        <v>612</v>
+      </c>
+      <c r="E211" t="s">
         <v>623</v>
-      </c>
-      <c r="B211" t="s">
-        <v>48</v>
-      </c>
-      <c r="D211" t="s">
-        <v>619</v>
-      </c>
-      <c r="E211" t="s">
-        <v>624</v>
       </c>
       <c r="F211" s="1">
         <v>46245</v>
@@ -7447,16 +7429,16 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
+        <v>624</v>
+      </c>
+      <c r="B212" t="s">
         <v>625</v>
       </c>
-      <c r="B212" t="s">
+      <c r="D212" t="s">
+        <v>612</v>
+      </c>
+      <c r="E212" t="s">
         <v>626</v>
-      </c>
-      <c r="D212" t="s">
-        <v>619</v>
-      </c>
-      <c r="E212" t="s">
-        <v>627</v>
       </c>
       <c r="F212" s="1">
         <v>46245</v>
@@ -7464,16 +7446,16 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
+        <v>627</v>
+      </c>
+      <c r="B213" t="s">
         <v>628</v>
       </c>
-      <c r="B213" t="s">
+      <c r="D213" t="s">
+        <v>612</v>
+      </c>
+      <c r="E213" t="s">
         <v>629</v>
-      </c>
-      <c r="D213" t="s">
-        <v>619</v>
-      </c>
-      <c r="E213" t="s">
-        <v>630</v>
       </c>
       <c r="F213" s="1">
         <v>46245</v>
@@ -7481,16 +7463,16 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
+        <v>630</v>
+      </c>
+      <c r="B214" t="s">
         <v>631</v>
       </c>
-      <c r="B214" t="s">
+      <c r="D214" t="s">
+        <v>612</v>
+      </c>
+      <c r="E214" t="s">
         <v>632</v>
-      </c>
-      <c r="D214" t="s">
-        <v>619</v>
-      </c>
-      <c r="E214" t="s">
-        <v>633</v>
       </c>
       <c r="F214" s="1">
         <v>46245</v>
@@ -7498,16 +7480,16 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
+        <v>633</v>
+      </c>
+      <c r="B215" t="s">
         <v>634</v>
       </c>
-      <c r="B215" t="s">
+      <c r="D215" t="s">
+        <v>634</v>
+      </c>
+      <c r="E215" t="s">
         <v>635</v>
-      </c>
-      <c r="D215" t="s">
-        <v>619</v>
-      </c>
-      <c r="E215" t="s">
-        <v>636</v>
       </c>
       <c r="F215" s="1">
         <v>46245</v>
@@ -7515,16 +7497,16 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
+        <v>636</v>
+      </c>
+      <c r="B216" t="s">
+        <v>634</v>
+      </c>
+      <c r="D216" t="s">
+        <v>634</v>
+      </c>
+      <c r="E216" t="s">
         <v>637</v>
-      </c>
-      <c r="B216" t="s">
-        <v>638</v>
-      </c>
-      <c r="D216" t="s">
-        <v>619</v>
-      </c>
-      <c r="E216" t="s">
-        <v>639</v>
       </c>
       <c r="F216" s="1">
         <v>46245</v>
@@ -7532,16 +7514,16 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
+        <v>638</v>
+      </c>
+      <c r="B217" t="s">
+        <v>639</v>
+      </c>
+      <c r="D217" t="s">
+        <v>612</v>
+      </c>
+      <c r="E217" t="s">
         <v>640</v>
-      </c>
-      <c r="B217" t="s">
-        <v>641</v>
-      </c>
-      <c r="D217" t="s">
-        <v>641</v>
-      </c>
-      <c r="E217" t="s">
-        <v>642</v>
       </c>
       <c r="F217" s="1">
         <v>46245</v>
@@ -7549,16 +7531,16 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B218" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="D218" t="s">
-        <v>641</v>
+        <v>612</v>
       </c>
       <c r="E218" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F218" s="1">
         <v>46245</v>
@@ -7566,16 +7548,16 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
+        <v>643</v>
+      </c>
+      <c r="B219" t="s">
+        <v>644</v>
+      </c>
+      <c r="D219" t="s">
+        <v>612</v>
+      </c>
+      <c r="E219" t="s">
         <v>645</v>
-      </c>
-      <c r="B219" t="s">
-        <v>646</v>
-      </c>
-      <c r="D219" t="s">
-        <v>619</v>
-      </c>
-      <c r="E219" t="s">
-        <v>647</v>
       </c>
       <c r="F219" s="1">
         <v>46245</v>
@@ -7583,16 +7565,16 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
+        <v>646</v>
+      </c>
+      <c r="B220" t="s">
+        <v>647</v>
+      </c>
+      <c r="D220" t="s">
+        <v>612</v>
+      </c>
+      <c r="E220" t="s">
         <v>648</v>
-      </c>
-      <c r="B220" t="s">
-        <v>635</v>
-      </c>
-      <c r="D220" t="s">
-        <v>619</v>
-      </c>
-      <c r="E220" t="s">
-        <v>649</v>
       </c>
       <c r="F220" s="1">
         <v>46245</v>
@@ -7600,16 +7582,16 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
+        <v>649</v>
+      </c>
+      <c r="B221" t="s">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>612</v>
+      </c>
+      <c r="E221" t="s">
         <v>650</v>
-      </c>
-      <c r="B221" t="s">
-        <v>651</v>
-      </c>
-      <c r="D221" t="s">
-        <v>619</v>
-      </c>
-      <c r="E221" t="s">
-        <v>652</v>
       </c>
       <c r="F221" s="1">
         <v>46245</v>
@@ -7617,16 +7599,16 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B222" t="s">
-        <v>654</v>
+        <v>625</v>
       </c>
       <c r="D222" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="E222" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F222" s="1">
         <v>46245</v>
@@ -7634,16 +7616,16 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B223" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="D223" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="E223" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="F223" s="1">
         <v>46245</v>
@@ -7651,16 +7633,16 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
+        <v>655</v>
+      </c>
+      <c r="B224" t="s">
+        <v>656</v>
+      </c>
+      <c r="D224" t="s">
+        <v>657</v>
+      </c>
+      <c r="E224" t="s">
         <v>658</v>
-      </c>
-      <c r="B224" t="s">
-        <v>646</v>
-      </c>
-      <c r="D224" t="s">
-        <v>619</v>
-      </c>
-      <c r="E224" t="s">
-        <v>659</v>
       </c>
       <c r="F224" s="1">
         <v>46245</v>
@@ -7668,16 +7650,16 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
+        <v>659</v>
+      </c>
+      <c r="B225" t="s">
+        <v>656</v>
+      </c>
+      <c r="D225" t="s">
+        <v>657</v>
+      </c>
+      <c r="E225" t="s">
         <v>660</v>
-      </c>
-      <c r="B225" t="s">
-        <v>661</v>
-      </c>
-      <c r="D225" t="s">
-        <v>662</v>
-      </c>
-      <c r="E225" t="s">
-        <v>663</v>
       </c>
       <c r="F225" s="1">
         <v>46245</v>
@@ -7685,16 +7667,16 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B226" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D226" t="s">
+        <v>657</v>
+      </c>
+      <c r="E226" t="s">
         <v>662</v>
-      </c>
-      <c r="E226" t="s">
-        <v>665</v>
       </c>
       <c r="F226" s="1">
         <v>46245</v>
@@ -7702,16 +7684,16 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B227" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D227" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E227" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="F227" s="1">
         <v>46245</v>
@@ -7719,16 +7701,16 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="B228" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D228" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E228" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="F228" s="1">
         <v>46245</v>
@@ -7736,16 +7718,16 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B229" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D229" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E229" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F229" s="1">
         <v>46245</v>
@@ -7753,16 +7735,16 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B230" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D230" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E230" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="F230" s="1">
         <v>46245</v>
@@ -7770,16 +7752,16 @@
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B231" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D231" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E231" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="F231" s="1">
         <v>46245</v>
@@ -7787,16 +7769,16 @@
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B232" t="s">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="D232" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E232" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F232" s="1">
         <v>46245</v>
@@ -7804,16 +7786,16 @@
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B233" t="s">
-        <v>679</v>
+        <v>656</v>
       </c>
       <c r="D233" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E233" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="F233" s="1">
         <v>46245</v>
@@ -7821,16 +7803,16 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B234" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D234" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E234" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="F234" s="1">
         <v>46245</v>
@@ -7838,16 +7820,16 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B235" t="s">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="D235" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E235" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="F235" s="1">
         <v>46245</v>
@@ -7855,16 +7837,16 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B236" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="D236" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E236" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="F236" s="1">
         <v>46245</v>
@@ -7872,16 +7854,16 @@
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B237" t="s">
-        <v>679</v>
+        <v>656</v>
       </c>
       <c r="D237" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E237" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="F237" s="1">
         <v>46245</v>
@@ -7889,16 +7871,16 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B238" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D238" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E238" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="F238" s="1">
         <v>46245</v>
@@ -7906,16 +7888,16 @@
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B239" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D239" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E239" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="F239" s="1">
         <v>46245</v>
@@ -7923,16 +7905,16 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B240" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D240" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E240" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="F240" s="1">
         <v>46245</v>
@@ -7940,16 +7922,16 @@
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B241" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D241" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E241" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F241" s="1">
         <v>46245</v>
@@ -7957,16 +7939,16 @@
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B242" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D242" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E242" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="F242" s="1">
         <v>46245</v>
@@ -7974,16 +7956,16 @@
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B243" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D243" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E243" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="F243" s="1">
         <v>46245</v>
@@ -7991,16 +7973,16 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B244" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D244" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E244" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="F244" s="1">
         <v>46245</v>
@@ -8008,16 +7990,16 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B245" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D245" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E245" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F245" s="1">
         <v>46245</v>
@@ -8025,16 +8007,16 @@
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B246" t="s">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="D246" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E246" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="F246" s="1">
         <v>46245</v>
@@ -8042,16 +8024,16 @@
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B247" t="s">
-        <v>679</v>
+        <v>656</v>
       </c>
       <c r="D247" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E247" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="F247" s="1">
         <v>46245</v>
@@ -8059,16 +8041,16 @@
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B248" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D248" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E248" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F248" s="1">
         <v>46245</v>
@@ -8076,16 +8058,16 @@
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B249" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D249" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E249" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F249" s="1">
         <v>46245</v>
@@ -8093,16 +8075,16 @@
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B250" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D250" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E250" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F250" s="1">
         <v>46245</v>
@@ -8110,16 +8092,16 @@
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B251" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D251" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E251" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F251" s="1">
         <v>46245</v>
@@ -8127,16 +8109,16 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
+        <v>714</v>
+      </c>
+      <c r="B252" t="s">
+        <v>715</v>
+      </c>
+      <c r="D252" t="s">
+        <v>716</v>
+      </c>
+      <c r="E252" t="s">
         <v>717</v>
-      </c>
-      <c r="B252" t="s">
-        <v>661</v>
-      </c>
-      <c r="D252" t="s">
-        <v>662</v>
-      </c>
-      <c r="E252" t="s">
-        <v>718</v>
       </c>
       <c r="F252" s="1">
         <v>46245</v>
@@ -8144,16 +8126,16 @@
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B253" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="D253" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="E253" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="F253" s="1">
         <v>46245</v>
@@ -8161,16 +8143,16 @@
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B254" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="D254" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="E254" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="F254" s="1">
         <v>46245</v>
@@ -8178,16 +8160,16 @@
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B255" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="D255" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="E255" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="F255" s="1">
         <v>46245</v>
@@ -8195,16 +8177,16 @@
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B256" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D256" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E256" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F256" s="1">
         <v>46245</v>
@@ -8212,16 +8194,16 @@
     </row>
     <row r="257" spans="1:6">
       <c r="A257" t="s">
+        <v>725</v>
+      </c>
+      <c r="B257" t="s">
+        <v>722</v>
+      </c>
+      <c r="D257" t="s">
+        <v>723</v>
+      </c>
+      <c r="E257" t="s">
         <v>726</v>
-      </c>
-      <c r="B257" t="s">
-        <v>727</v>
-      </c>
-      <c r="D257" t="s">
-        <v>728</v>
-      </c>
-      <c r="E257" t="s">
-        <v>729</v>
       </c>
       <c r="F257" s="1">
         <v>46245</v>
@@ -8229,16 +8211,16 @@
     </row>
     <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B258" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D258" t="s">
+        <v>723</v>
+      </c>
+      <c r="E258" t="s">
         <v>728</v>
-      </c>
-      <c r="E258" t="s">
-        <v>731</v>
       </c>
       <c r="F258" s="1">
         <v>46245</v>
@@ -8246,16 +8228,16 @@
     </row>
     <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B259" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D259" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="E259" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="F259" s="1">
         <v>46245</v>
@@ -8263,16 +8245,16 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B260" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D260" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="E260" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="F260" s="1">
         <v>46245</v>
@@ -8280,16 +8262,16 @@
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B261" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D261" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="E261" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="F261" s="1">
         <v>46245</v>
@@ -8297,16 +8279,16 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B262" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D262" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="E262" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F262" s="1">
         <v>46245</v>
@@ -8314,16 +8296,19 @@
     </row>
     <row r="263" spans="1:6">
       <c r="A263" t="s">
+        <v>737</v>
+      </c>
+      <c r="B263" t="s">
+        <v>738</v>
+      </c>
+      <c r="C263" t="s">
+        <v>145</v>
+      </c>
+      <c r="D263" t="s">
+        <v>739</v>
+      </c>
+      <c r="E263" t="s">
         <v>740</v>
-      </c>
-      <c r="B263" t="s">
-        <v>727</v>
-      </c>
-      <c r="D263" t="s">
-        <v>728</v>
-      </c>
-      <c r="E263" t="s">
-        <v>741</v>
       </c>
       <c r="F263" s="1">
         <v>46245</v>
@@ -8331,19 +8316,19 @@
     </row>
     <row r="264" spans="1:6">
       <c r="A264" t="s">
+        <v>741</v>
+      </c>
+      <c r="B264" t="s">
+        <v>738</v>
+      </c>
+      <c r="C264" t="s">
+        <v>176</v>
+      </c>
+      <c r="D264" t="s">
+        <v>739</v>
+      </c>
+      <c r="E264" t="s">
         <v>742</v>
-      </c>
-      <c r="B264" t="s">
-        <v>743</v>
-      </c>
-      <c r="C264" t="s">
-        <v>141</v>
-      </c>
-      <c r="D264" t="s">
-        <v>744</v>
-      </c>
-      <c r="E264" t="s">
-        <v>745</v>
       </c>
       <c r="F264" s="1">
         <v>46245</v>
@@ -8351,19 +8336,19 @@
     </row>
     <row r="265" spans="1:6">
       <c r="A265" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B265" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C265" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D265" t="s">
+        <v>739</v>
+      </c>
+      <c r="E265" t="s">
         <v>744</v>
-      </c>
-      <c r="E265" t="s">
-        <v>747</v>
       </c>
       <c r="F265" s="1">
         <v>46245</v>
@@ -8371,19 +8356,19 @@
     </row>
     <row r="266" spans="1:6">
       <c r="A266" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B266" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C266" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="D266" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="E266" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="F266" s="1">
         <v>46245</v>
@@ -8391,19 +8376,19 @@
     </row>
     <row r="267" spans="1:6">
       <c r="A267" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B267" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C267" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D267" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="E267" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="F267" s="1">
         <v>46245</v>
@@ -8411,19 +8396,19 @@
     </row>
     <row r="268" spans="1:6">
       <c r="A268" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B268" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C268" t="s">
-        <v>100</v>
+        <v>185</v>
       </c>
       <c r="D268" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="E268" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="F268" s="1">
         <v>46245</v>
@@ -8431,19 +8416,19 @@
     </row>
     <row r="269" spans="1:6">
       <c r="A269" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B269" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C269" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D269" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="E269" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F269" s="1">
         <v>46245</v>
@@ -8451,19 +8436,19 @@
     </row>
     <row r="270" spans="1:6">
       <c r="A270" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B270" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C270" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="D270" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="E270" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="F270" s="1">
         <v>46245</v>
@@ -8471,19 +8456,16 @@
     </row>
     <row r="271" spans="1:6">
       <c r="A271" t="s">
+        <v>755</v>
+      </c>
+      <c r="B271" t="s">
+        <v>756</v>
+      </c>
+      <c r="D271" t="s">
+        <v>757</v>
+      </c>
+      <c r="E271" t="s">
         <v>758</v>
-      </c>
-      <c r="B271" t="s">
-        <v>743</v>
-      </c>
-      <c r="C271" t="s">
-        <v>141</v>
-      </c>
-      <c r="D271" t="s">
-        <v>744</v>
-      </c>
-      <c r="E271" t="s">
-        <v>759</v>
       </c>
       <c r="F271" s="1">
         <v>46245</v>
@@ -8491,16 +8473,16 @@
     </row>
     <row r="272" spans="1:6">
       <c r="A272" t="s">
+        <v>759</v>
+      </c>
+      <c r="B272" t="s">
         <v>760</v>
       </c>
-      <c r="B272" t="s">
+      <c r="D272" t="s">
         <v>761</v>
       </c>
-      <c r="D272" t="s">
+      <c r="E272" t="s">
         <v>762</v>
-      </c>
-      <c r="E272" t="s">
-        <v>763</v>
       </c>
       <c r="F272" s="1">
         <v>46245</v>
@@ -8508,16 +8490,16 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" t="s">
+        <v>763</v>
+      </c>
+      <c r="B273" t="s">
         <v>764</v>
       </c>
-      <c r="B273" t="s">
+      <c r="D273" t="s">
+        <v>761</v>
+      </c>
+      <c r="E273" t="s">
         <v>765</v>
-      </c>
-      <c r="D273" t="s">
-        <v>766</v>
-      </c>
-      <c r="E273" t="s">
-        <v>767</v>
       </c>
       <c r="F273" s="1">
         <v>46245</v>
@@ -8525,16 +8507,16 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B274" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="D274" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="E274" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="F274" s="1">
         <v>46245</v>
@@ -8542,16 +8524,16 @@
     </row>
     <row r="275" spans="1:6">
       <c r="A275" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="B275" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="D275" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="E275" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="F275" s="1">
         <v>46245</v>
@@ -8559,16 +8541,16 @@
     </row>
     <row r="276" spans="1:6">
       <c r="A276" t="s">
+        <v>769</v>
+      </c>
+      <c r="B276" t="s">
+        <v>770</v>
+      </c>
+      <c r="D276" t="s">
         <v>771</v>
       </c>
-      <c r="B276" t="s">
-        <v>765</v>
-      </c>
-      <c r="D276" t="s">
-        <v>766</v>
-      </c>
       <c r="E276" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F276" s="1">
         <v>46245</v>
@@ -8576,16 +8558,16 @@
     </row>
     <row r="277" spans="1:6">
       <c r="A277" t="s">
+        <v>773</v>
+      </c>
+      <c r="B277" t="s">
+        <v>756</v>
+      </c>
+      <c r="D277" t="s">
+        <v>757</v>
+      </c>
+      <c r="E277" t="s">
         <v>774</v>
-      </c>
-      <c r="B277" t="s">
-        <v>775</v>
-      </c>
-      <c r="D277" t="s">
-        <v>776</v>
-      </c>
-      <c r="E277" t="s">
-        <v>777</v>
       </c>
       <c r="F277" s="1">
         <v>46245</v>
@@ -8593,16 +8575,16 @@
     </row>
     <row r="278" spans="1:6">
       <c r="A278" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B278" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D278" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E278" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="F278" s="1">
         <v>46245</v>
@@ -8610,16 +8592,16 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B279" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D279" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E279" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="F279" s="1">
         <v>46245</v>
@@ -8627,16 +8609,16 @@
     </row>
     <row r="280" spans="1:6">
       <c r="A280" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B280" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="D280" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="E280" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="F280" s="1">
         <v>46245</v>
@@ -8644,16 +8626,16 @@
     </row>
     <row r="281" spans="1:6">
       <c r="A281" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B281" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
       <c r="D281" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="E281" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="F281" s="1">
         <v>46245</v>
@@ -8661,16 +8643,16 @@
     </row>
     <row r="282" spans="1:6">
       <c r="A282" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B282" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="D282" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="E282" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="F282" s="1">
         <v>46245</v>
@@ -8678,16 +8660,16 @@
     </row>
     <row r="283" spans="1:6">
       <c r="A283" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B283" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D283" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E283" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="F283" s="1">
         <v>46245</v>
@@ -8695,16 +8677,16 @@
     </row>
     <row r="284" spans="1:6">
       <c r="A284" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B284" t="s">
+        <v>760</v>
+      </c>
+      <c r="D284" t="s">
         <v>761</v>
       </c>
-      <c r="D284" t="s">
-        <v>762</v>
-      </c>
       <c r="E284" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="F284" s="1">
         <v>46245</v>
@@ -8712,16 +8694,16 @@
     </row>
     <row r="285" spans="1:6">
       <c r="A285" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B285" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="D285" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="E285" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="F285" s="1">
         <v>46245</v>
@@ -8729,16 +8711,16 @@
     </row>
     <row r="286" spans="1:6">
       <c r="A286" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B286" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="D286" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="E286" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="F286" s="1">
         <v>46245</v>
@@ -8746,16 +8728,16 @@
     </row>
     <row r="287" spans="1:6">
       <c r="A287" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B287" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="D287" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="E287" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="F287" s="1">
         <v>46245</v>
@@ -8763,16 +8745,16 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B288" t="s">
-        <v>775</v>
+        <v>756</v>
       </c>
       <c r="D288" t="s">
-        <v>776</v>
+        <v>757</v>
       </c>
       <c r="E288" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="F288" s="1">
         <v>46245</v>
@@ -8780,16 +8762,16 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B289" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D289" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E289" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="F289" s="1">
         <v>46245</v>
@@ -8797,16 +8779,16 @@
     </row>
     <row r="290" spans="1:6">
       <c r="A290" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B290" t="s">
+        <v>764</v>
+      </c>
+      <c r="D290" t="s">
         <v>761</v>
       </c>
-      <c r="D290" t="s">
-        <v>762</v>
-      </c>
       <c r="E290" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="F290" s="1">
         <v>46245</v>
@@ -8814,16 +8796,16 @@
     </row>
     <row r="291" spans="1:6">
       <c r="A291" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B291" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="D291" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="E291" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="F291" s="1">
         <v>46245</v>
@@ -8831,16 +8813,16 @@
     </row>
     <row r="292" spans="1:6">
       <c r="A292" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B292" t="s">
+        <v>760</v>
+      </c>
+      <c r="D292" t="s">
         <v>761</v>
       </c>
-      <c r="D292" t="s">
-        <v>762</v>
-      </c>
       <c r="E292" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="F292" s="1">
         <v>46245</v>
@@ -8848,16 +8830,16 @@
     </row>
     <row r="293" spans="1:6">
       <c r="A293" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B293" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="D293" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="E293" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="F293" s="1">
         <v>46245</v>
@@ -8865,16 +8847,16 @@
     </row>
     <row r="294" spans="1:6">
       <c r="A294" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B294" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D294" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E294" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="F294" s="1">
         <v>46245</v>
@@ -8882,16 +8864,16 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B295" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D295" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E295" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="F295" s="1">
         <v>46245</v>
@@ -8899,16 +8881,16 @@
     </row>
     <row r="296" spans="1:6">
       <c r="A296" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B296" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D296" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E296" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="F296" s="1">
         <v>46245</v>
@@ -8916,16 +8898,16 @@
     </row>
     <row r="297" spans="1:6">
       <c r="A297" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B297" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D297" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E297" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="F297" s="1">
         <v>46245</v>
@@ -8933,16 +8915,16 @@
     </row>
     <row r="298" spans="1:6">
       <c r="A298" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B298" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D298" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E298" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="F298" s="1">
         <v>46245</v>
@@ -8950,16 +8932,16 @@
     </row>
     <row r="299" spans="1:6">
       <c r="A299" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B299" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D299" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E299" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F299" s="1">
         <v>46245</v>
@@ -8967,16 +8949,16 @@
     </row>
     <row r="300" spans="1:6">
       <c r="A300" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B300" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D300" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E300" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="F300" s="1">
         <v>46245</v>
@@ -8984,16 +8966,16 @@
     </row>
     <row r="301" spans="1:6">
       <c r="A301" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B301" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D301" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E301" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="F301" s="1">
         <v>46245</v>
@@ -9001,16 +8983,16 @@
     </row>
     <row r="302" spans="1:6">
       <c r="A302" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="B302" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D302" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E302" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="F302" s="1">
         <v>46245</v>
@@ -9018,16 +9000,16 @@
     </row>
     <row r="303" spans="1:6">
       <c r="A303" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B303" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D303" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E303" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="F303" s="1">
         <v>46245</v>
@@ -9035,16 +9017,16 @@
     </row>
     <row r="304" spans="1:6">
       <c r="A304" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="B304" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D304" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E304" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="F304" s="1">
         <v>46245</v>
@@ -9052,16 +9034,16 @@
     </row>
     <row r="305" spans="1:6">
       <c r="A305" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B305" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D305" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E305" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="F305" s="1">
         <v>46245</v>
@@ -9069,16 +9051,16 @@
     </row>
     <row r="306" spans="1:6">
       <c r="A306" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="B306" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D306" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E306" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="F306" s="1">
         <v>46245</v>
@@ -9086,16 +9068,16 @@
     </row>
     <row r="307" spans="1:6">
       <c r="A307" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B307" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D307" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E307" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="F307" s="1">
         <v>46245</v>
@@ -9103,16 +9085,16 @@
     </row>
     <row r="308" spans="1:6">
       <c r="A308" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="B308" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="D308" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="E308" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="F308" s="1">
         <v>46245</v>
@@ -9120,16 +9102,16 @@
     </row>
     <row r="309" spans="1:6">
       <c r="A309" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B309" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D309" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="E309" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="F309" s="1">
         <v>46245</v>
@@ -9137,16 +9119,16 @@
     </row>
     <row r="310" spans="1:6">
       <c r="A310" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B310" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="D310" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="E310" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="F310" s="1">
         <v>46245</v>
@@ -9154,16 +9136,16 @@
     </row>
     <row r="311" spans="1:6">
       <c r="A311" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="B311" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="D311" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="E311" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="F311" s="1">
         <v>46245</v>
@@ -9171,16 +9153,16 @@
     </row>
     <row r="312" spans="1:6">
       <c r="A312" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="B312" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="D312" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="E312" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="F312" s="1">
         <v>46245</v>
@@ -9188,16 +9170,16 @@
     </row>
     <row r="313" spans="1:6">
       <c r="A313" t="s">
+        <v>846</v>
+      </c>
+      <c r="B313" t="s">
+        <v>847</v>
+      </c>
+      <c r="D313" t="s">
+        <v>848</v>
+      </c>
+      <c r="E313" t="s">
         <v>849</v>
-      </c>
-      <c r="B313" t="s">
-        <v>850</v>
-      </c>
-      <c r="D313" t="s">
-        <v>851</v>
-      </c>
-      <c r="E313" t="s">
-        <v>852</v>
       </c>
       <c r="F313" s="1">
         <v>46245</v>
@@ -9205,16 +9187,16 @@
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B314" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D314" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E314" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F314" s="1">
         <v>46245</v>
@@ -9222,16 +9204,16 @@
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B315" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D315" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E315" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F315" s="1">
         <v>46245</v>
@@ -9239,16 +9221,16 @@
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="B316" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D316" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E316" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F316" s="1">
         <v>46245</v>
@@ -9256,16 +9238,16 @@
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B317" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D317" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E317" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F317" s="1">
         <v>46245</v>
@@ -9273,16 +9255,16 @@
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="B318" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D318" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E318" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F318" s="1">
         <v>46245</v>
@@ -9290,16 +9272,16 @@
     </row>
     <row r="319" spans="1:6">
       <c r="A319" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B319" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D319" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E319" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F319" s="1">
         <v>46245</v>
@@ -9307,16 +9289,16 @@
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B320" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D320" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E320" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F320" s="1">
         <v>46245</v>
@@ -9324,16 +9306,16 @@
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="B321" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D321" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E321" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F321" s="1">
         <v>46245</v>
@@ -9341,16 +9323,16 @@
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="B322" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D322" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E322" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F322" s="1">
         <v>46245</v>
@@ -9358,16 +9340,16 @@
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B323" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D323" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E323" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F323" s="1">
         <v>46245</v>
@@ -9375,16 +9357,16 @@
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="B324" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D324" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E324" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F324" s="1">
         <v>46245</v>
@@ -9392,16 +9374,16 @@
     </row>
     <row r="325" spans="1:6">
       <c r="A325" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B325" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D325" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E325" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F325" s="1">
         <v>46245</v>
@@ -9409,16 +9391,16 @@
     </row>
     <row r="326" spans="1:6">
       <c r="A326" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B326" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D326" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E326" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F326" s="1">
         <v>46245</v>
@@ -9426,16 +9408,16 @@
     </row>
     <row r="327" spans="1:6">
       <c r="A327" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B327" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D327" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E327" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="F327" s="1">
         <v>46245</v>
@@ -9443,16 +9425,16 @@
     </row>
     <row r="328" spans="1:6">
       <c r="A328" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="B328" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="D328" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E328" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="F328" s="1">
         <v>46245</v>
@@ -9460,16 +9442,16 @@
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="B329" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="D329" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E329" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="F329" s="1">
         <v>46245</v>
@@ -9477,16 +9459,16 @@
     </row>
     <row r="330" spans="1:6">
       <c r="A330" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B330" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D330" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E330" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="F330" s="1">
         <v>46245</v>
@@ -9494,16 +9476,16 @@
     </row>
     <row r="331" spans="1:6">
       <c r="A331" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B331" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="D331" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E331" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="F331" s="1">
         <v>46245</v>
@@ -9511,16 +9493,16 @@
     </row>
     <row r="332" spans="1:6">
       <c r="A332" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="B332" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="D332" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E332" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="F332" s="1">
         <v>46245</v>
@@ -9528,19 +9510,19 @@
     </row>
     <row r="333" spans="1:6">
       <c r="A333" t="s">
+        <v>877</v>
+      </c>
+      <c r="B333" t="s">
+        <v>878</v>
+      </c>
+      <c r="C333" t="s">
+        <v>89</v>
+      </c>
+      <c r="D333" t="s">
+        <v>879</v>
+      </c>
+      <c r="E333" t="s">
         <v>880</v>
-      </c>
-      <c r="B333" t="s">
-        <v>881</v>
-      </c>
-      <c r="C333" t="s">
-        <v>85</v>
-      </c>
-      <c r="D333" t="s">
-        <v>882</v>
-      </c>
-      <c r="E333" t="s">
-        <v>883</v>
       </c>
       <c r="F333" s="1">
         <v>46245</v>
@@ -9548,19 +9530,19 @@
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B334" t="s">
+        <v>878</v>
+      </c>
+      <c r="C334" t="s">
+        <v>231</v>
+      </c>
+      <c r="D334" t="s">
+        <v>879</v>
+      </c>
+      <c r="E334" t="s">
         <v>881</v>
-      </c>
-      <c r="C334" t="s">
-        <v>235</v>
-      </c>
-      <c r="D334" t="s">
-        <v>882</v>
-      </c>
-      <c r="E334" t="s">
-        <v>884</v>
       </c>
       <c r="F334" s="1">
         <v>46245</v>
@@ -9568,19 +9550,19 @@
     </row>
     <row r="335" spans="1:6">
       <c r="A335" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="B335" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="C335" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D335" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="E335" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="F335" s="1">
         <v>46245</v>
@@ -9588,19 +9570,19 @@
     </row>
     <row r="336" spans="1:6">
       <c r="A336" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="B336" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="C336" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="D336" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="E336" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="F336" s="1">
         <v>46245</v>
@@ -9608,16 +9590,16 @@
     </row>
     <row r="337" spans="1:6">
       <c r="A337" t="s">
+        <v>887</v>
+      </c>
+      <c r="B337" t="s">
+        <v>888</v>
+      </c>
+      <c r="D337" t="s">
+        <v>889</v>
+      </c>
+      <c r="E337" t="s">
         <v>890</v>
-      </c>
-      <c r="B337" t="s">
-        <v>891</v>
-      </c>
-      <c r="D337" t="s">
-        <v>892</v>
-      </c>
-      <c r="E337" t="s">
-        <v>893</v>
       </c>
       <c r="F337" s="1">
         <v>46245</v>
@@ -9625,16 +9607,16 @@
     </row>
     <row r="338" spans="1:6">
       <c r="A338" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B338" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D338" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E338" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F338" s="1">
         <v>46245</v>
@@ -9642,16 +9624,16 @@
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="B339" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D339" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E339" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F339" s="1">
         <v>46245</v>
@@ -9659,16 +9641,16 @@
     </row>
     <row r="340" spans="1:6">
       <c r="A340" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="B340" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D340" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E340" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F340" s="1">
         <v>46245</v>
@@ -9676,16 +9658,16 @@
     </row>
     <row r="341" spans="1:6">
       <c r="A341" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B341" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D341" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E341" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F341" s="1">
         <v>46245</v>
@@ -9693,16 +9675,16 @@
     </row>
     <row r="342" spans="1:6">
       <c r="A342" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B342" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D342" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E342" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F342" s="1">
         <v>46245</v>
@@ -9710,16 +9692,16 @@
     </row>
     <row r="343" spans="1:6">
       <c r="A343" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="B343" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D343" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E343" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F343" s="1">
         <v>46245</v>
@@ -9727,16 +9709,16 @@
     </row>
     <row r="344" spans="1:6">
       <c r="A344" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="B344" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D344" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E344" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F344" s="1">
         <v>46245</v>
@@ -9744,16 +9726,16 @@
     </row>
     <row r="345" spans="1:6">
       <c r="A345" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="B345" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D345" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E345" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F345" s="1">
         <v>46245</v>
@@ -9761,16 +9743,16 @@
     </row>
     <row r="346" spans="1:6">
       <c r="A346" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="B346" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D346" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E346" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F346" s="1">
         <v>46245</v>
@@ -9778,16 +9760,16 @@
     </row>
     <row r="347" spans="1:6">
       <c r="A347" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="B347" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D347" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E347" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F347" s="1">
         <v>46245</v>
@@ -9795,16 +9777,16 @@
     </row>
     <row r="348" spans="1:6">
       <c r="A348" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="B348" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D348" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E348" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F348" s="1">
         <v>46245</v>
@@ -9812,16 +9794,16 @@
     </row>
     <row r="349" spans="1:6">
       <c r="A349" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B349" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D349" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E349" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F349" s="1">
         <v>46245</v>
@@ -9829,16 +9811,16 @@
     </row>
     <row r="350" spans="1:6">
       <c r="A350" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B350" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D350" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E350" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F350" s="1">
         <v>46245</v>
@@ -9846,16 +9828,16 @@
     </row>
     <row r="351" spans="1:6">
       <c r="A351" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B351" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D351" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E351" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F351" s="1">
         <v>46245</v>
@@ -9863,16 +9845,16 @@
     </row>
     <row r="352" spans="1:6">
       <c r="A352" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B352" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="D352" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E352" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F352" s="1">
         <v>46245</v>
@@ -9880,16 +9862,16 @@
     </row>
     <row r="353" spans="1:6">
       <c r="A353" t="s">
+        <v>906</v>
+      </c>
+      <c r="B353" t="s">
+        <v>907</v>
+      </c>
+      <c r="D353" t="s">
+        <v>908</v>
+      </c>
+      <c r="E353" t="s">
         <v>909</v>
-      </c>
-      <c r="B353" t="s">
-        <v>891</v>
-      </c>
-      <c r="D353" t="s">
-        <v>892</v>
-      </c>
-      <c r="E353" t="s">
-        <v>893</v>
       </c>
       <c r="F353" s="1">
         <v>46245</v>
@@ -9900,13 +9882,13 @@
         <v>910</v>
       </c>
       <c r="B354" t="s">
+        <v>907</v>
+      </c>
+      <c r="D354" t="s">
+        <v>908</v>
+      </c>
+      <c r="E354" t="s">
         <v>911</v>
-      </c>
-      <c r="D354" t="s">
-        <v>912</v>
-      </c>
-      <c r="E354" t="s">
-        <v>913</v>
       </c>
       <c r="F354" s="1">
         <v>46245</v>
@@ -9914,16 +9896,16 @@
     </row>
     <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B355" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D355" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="E355" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="F355" s="1">
         <v>46245</v>
@@ -9931,16 +9913,16 @@
     </row>
     <row r="356" spans="1:6">
       <c r="A356" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B356" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D356" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="E356" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="F356" s="1">
         <v>46245</v>
@@ -9948,13 +9930,13 @@
     </row>
     <row r="357" spans="1:6">
       <c r="A357" t="s">
+        <v>916</v>
+      </c>
+      <c r="B357" t="s">
+        <v>917</v>
+      </c>
+      <c r="D357" t="s">
         <v>918</v>
-      </c>
-      <c r="B357" t="s">
-        <v>911</v>
-      </c>
-      <c r="D357" t="s">
-        <v>912</v>
       </c>
       <c r="E357" t="s">
         <v>919</v>
@@ -9985,13 +9967,13 @@
         <v>924</v>
       </c>
       <c r="B359" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="D359" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="E359" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="F359" s="1">
         <v>46245</v>
@@ -9999,16 +9981,16 @@
     </row>
     <row r="360" spans="1:6">
       <c r="A360" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B360" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="D360" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="E360" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="F360" s="1">
         <v>46245</v>
@@ -10016,16 +9998,16 @@
     </row>
     <row r="361" spans="1:6">
       <c r="A361" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B361" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="D361" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="E361" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="F361" s="1">
         <v>46245</v>
@@ -10033,16 +10015,16 @@
     </row>
     <row r="362" spans="1:6">
       <c r="A362" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B362" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="D362" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="E362" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="F362" s="1">
         <v>46245</v>
@@ -10050,16 +10032,16 @@
     </row>
     <row r="363" spans="1:6">
       <c r="A363" t="s">
+        <v>928</v>
+      </c>
+      <c r="B363" t="s">
+        <v>929</v>
+      </c>
+      <c r="D363" t="s">
+        <v>930</v>
+      </c>
+      <c r="E363" t="s">
         <v>931</v>
-      </c>
-      <c r="B363" t="s">
-        <v>925</v>
-      </c>
-      <c r="D363" t="s">
-        <v>926</v>
-      </c>
-      <c r="E363" t="s">
-        <v>927</v>
       </c>
       <c r="F363" s="1">
         <v>46245</v>
@@ -10070,13 +10052,13 @@
         <v>932</v>
       </c>
       <c r="B364" t="s">
+        <v>929</v>
+      </c>
+      <c r="D364" t="s">
+        <v>930</v>
+      </c>
+      <c r="E364" t="s">
         <v>933</v>
-      </c>
-      <c r="D364" t="s">
-        <v>934</v>
-      </c>
-      <c r="E364" t="s">
-        <v>935</v>
       </c>
       <c r="F364" s="1">
         <v>46245</v>
@@ -10084,16 +10066,16 @@
     </row>
     <row r="365" spans="1:6">
       <c r="A365" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B365" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D365" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E365" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="F365" s="1">
         <v>46245</v>
@@ -10101,16 +10083,16 @@
     </row>
     <row r="366" spans="1:6">
       <c r="A366" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B366" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D366" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E366" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="F366" s="1">
         <v>46245</v>
@@ -10118,16 +10100,16 @@
     </row>
     <row r="367" spans="1:6">
       <c r="A367" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B367" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D367" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E367" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="F367" s="1">
         <v>46245</v>
@@ -10135,16 +10117,16 @@
     </row>
     <row r="368" spans="1:6">
       <c r="A368" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B368" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D368" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E368" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="F368" s="1">
         <v>46245</v>
@@ -10152,16 +10134,16 @@
     </row>
     <row r="369" spans="1:6">
       <c r="A369" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B369" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D369" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E369" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="F369" s="1">
         <v>46245</v>
@@ -10169,16 +10151,16 @@
     </row>
     <row r="370" spans="1:6">
       <c r="A370" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B370" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D370" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E370" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="F370" s="1">
         <v>46245</v>
@@ -10186,16 +10168,16 @@
     </row>
     <row r="371" spans="1:6">
       <c r="A371" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B371" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D371" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E371" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="F371" s="1">
         <v>46245</v>
@@ -10203,16 +10185,16 @@
     </row>
     <row r="372" spans="1:6">
       <c r="A372" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B372" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D372" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E372" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="F372" s="1">
         <v>46245</v>
@@ -10220,35 +10202,18 @@
     </row>
     <row r="373" spans="1:6">
       <c r="A373" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B373" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D373" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="E373" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="F373" s="1">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="374" spans="1:6">
-      <c r="A374" t="s">
-        <v>954</v>
-      </c>
-      <c r="B374" t="s">
-        <v>933</v>
-      </c>
-      <c r="D374" t="s">
-        <v>934</v>
-      </c>
-      <c r="E374" t="s">
-        <v>955</v>
-      </c>
-      <c r="F374" s="1">
         <v>46245</v>
       </c>
     </row>

--- a/Archived_HE_Data/hedata_2026-08-11.xlsx
+++ b/Archived_HE_Data/hedata_2026-08-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="952">
   <si>
     <t>Title</t>
   </si>
@@ -49,1020 +49,1014 @@
     <t>https://jobs.montana.edu/postings/52557</t>
   </si>
   <si>
-    <t>Composite Research Engineer</t>
+    <t>Registered Dietitian Nutritionist</t>
+  </si>
+  <si>
+    <t>Athletics</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52554</t>
+  </si>
+  <si>
+    <t>Administrative Associate IV, Buffalo Nations</t>
+  </si>
+  <si>
+    <t>Food Systems Nutrition &amp; Kinesiolog</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52548</t>
+  </si>
+  <si>
+    <t>Graphic Designer</t>
+  </si>
+  <si>
+    <t>Museum of the Rockies</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52538</t>
+  </si>
+  <si>
+    <t>Academic Success Coordinator - Gianforte School of Computing</t>
+  </si>
+  <si>
+    <t>Gianforte School of Computing</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52532</t>
+  </si>
+  <si>
+    <t>Budget and Fiscal Manager</t>
+  </si>
+  <si>
+    <t>Graduate School</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52524</t>
+  </si>
+  <si>
+    <t>Academic Advisor II</t>
+  </si>
+  <si>
+    <t>MSSE MS Science Education</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52523</t>
+  </si>
+  <si>
+    <t>Instructional Technology Specialist</t>
+  </si>
+  <si>
+    <t>Center for Faculty Excellence</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52513</t>
+  </si>
+  <si>
+    <t>Mechanic II or III</t>
+  </si>
+  <si>
+    <t>Facility Services</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52507</t>
+  </si>
+  <si>
+    <t>Extension Agent - Fallon County</t>
+  </si>
+  <si>
+    <t>Extension Agents/Field</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Budget and Finance. </t>
+  </si>
+  <si>
+    <t>SWC AVP OPs</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52499</t>
+  </si>
+  <si>
+    <t>Extension Grant and Fiscal Coordinator</t>
+  </si>
+  <si>
+    <t>Administration - MSU Extension</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52498</t>
+  </si>
+  <si>
+    <t>Admissions Specialist</t>
+  </si>
+  <si>
+    <t>Admissions</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52495</t>
+  </si>
+  <si>
+    <t>Executive Director, QCORE</t>
+  </si>
+  <si>
+    <t>Physics</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52484</t>
+  </si>
+  <si>
+    <t>Computer Support Specialist II</t>
+  </si>
+  <si>
+    <t>College of Ag Team</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52483</t>
+  </si>
+  <si>
+    <t>Fire Marshal</t>
+  </si>
+  <si>
+    <t>Safety &amp; Risk Mgmt</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52482</t>
+  </si>
+  <si>
+    <t>Supply and Inventory Associate</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52476</t>
+  </si>
+  <si>
+    <t>Event Coordinator</t>
+  </si>
+  <si>
+    <t>Conference &amp; Event Services</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52471</t>
+  </si>
+  <si>
+    <t>University Studies Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>University Studies</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52467</t>
+  </si>
+  <si>
+    <t>Equipment Operator II</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52460</t>
+  </si>
+  <si>
+    <t>Turtle Island Tales Program Coordinator I</t>
+  </si>
+  <si>
+    <t>American Indian Rural Health Equity</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52453</t>
+  </si>
+  <si>
+    <t>Training and Development Specialist</t>
+  </si>
+  <si>
+    <t>DISC</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52451</t>
+  </si>
+  <si>
+    <t>Research Assistant III *Miles City-Fort Keogh*</t>
+  </si>
+  <si>
+    <t>AES LARRS</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52450</t>
+  </si>
+  <si>
+    <t>Senior Technology Manager</t>
+  </si>
+  <si>
+    <t>MSU Technology Transfer Office</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52448</t>
+  </si>
+  <si>
+    <t>Program Coordinator, Ivan Doig Center for the Study of the Lands &amp; Peoples of the North American West</t>
+  </si>
+  <si>
+    <t>Western Lands &amp; People Center</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52446</t>
+  </si>
+  <si>
+    <t>Assistant Director - Testing Services</t>
+  </si>
+  <si>
+    <t>University Testing Services</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52444</t>
+  </si>
+  <si>
+    <t>FLEX Academic Advisors - (Pooled Positions)</t>
+  </si>
+  <si>
+    <t>Advising Commons</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52443</t>
+  </si>
+  <si>
+    <t>Faculty Instructor &amp; Bracken Business Center Coach for the Jake Jabs College of Business &amp; Entrepreneurship Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Jabs Program Fee</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52440</t>
+  </si>
+  <si>
+    <t>Chief Marketing Officer</t>
+  </si>
+  <si>
+    <t>University Communications</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52438</t>
+  </si>
+  <si>
+    <t>Admissions Evaluator</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52435</t>
+  </si>
+  <si>
+    <t>Gen Ed – Health Sciences Non-Tenure Track Faculty – Gallatin College (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Gallatin College</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52430</t>
+  </si>
+  <si>
+    <t>Cook II (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Culinary Services Administration</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52423</t>
+  </si>
+  <si>
+    <t>Custodian II - Housing</t>
+  </si>
+  <si>
+    <t>Residence Life Administration</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52416</t>
+  </si>
+  <si>
+    <t>Career Education Coach</t>
+  </si>
+  <si>
+    <t>Career Services</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52413</t>
+  </si>
+  <si>
+    <t>Data Systems Manager</t>
+  </si>
+  <si>
+    <t>UIT Enterprise Services Group CUF</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52411</t>
+  </si>
+  <si>
+    <t>Grants and Fiscal Manager</t>
+  </si>
+  <si>
+    <t>Western Transportation Institute</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52409</t>
+  </si>
+  <si>
+    <t>Extension Agent – Agriculture and 4-H Youth Development – Pondera County</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52408</t>
+  </si>
+  <si>
+    <t>Extension Agent – Family and Consumer Sciences and 4-H Youth Development – Pondera County</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52407</t>
+  </si>
+  <si>
+    <t>Operator-In-Training</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52406</t>
+  </si>
+  <si>
+    <t>Academic Advisor I or II</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52404</t>
+  </si>
+  <si>
+    <t>Cook III (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52389</t>
+  </si>
+  <si>
+    <t>Budget and Fiscal Director</t>
+  </si>
+  <si>
+    <t>Dean Educ/HHD</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52369</t>
+  </si>
+  <si>
+    <t>Assistant Professor, Cropping System Agronomist *Havre, MT*</t>
+  </si>
+  <si>
+    <t>AES NARC</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52366</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52345</t>
+  </si>
+  <si>
+    <t>Computer Supp Spec II</t>
+  </si>
+  <si>
+    <t>College of L&amp;S Team</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52344</t>
+  </si>
+  <si>
+    <t>Floor Supervisor - Dining Halls</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52339</t>
+  </si>
+  <si>
+    <t>Early Childhood Classroom Support</t>
+  </si>
+  <si>
+    <t>Human Development &amp;Community Health</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52332</t>
+  </si>
+  <si>
+    <t>Research Associate/Research Scientist/Research Engineer</t>
+  </si>
+  <si>
+    <t>Spectrum Lab</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52331</t>
+  </si>
+  <si>
+    <t>Strategic Partnerships and Industry Relations Lead</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52326</t>
+  </si>
+  <si>
+    <t>Financial Associate</t>
+  </si>
+  <si>
+    <t>Fiscal Shared Services</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52323</t>
+  </si>
+  <si>
+    <t>Instructor of Architecture Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52318</t>
+  </si>
+  <si>
+    <t>Visiting Scholar - Architecture (Non-Tenure Track Faculty Applicant Pool)</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52317</t>
+  </si>
+  <si>
+    <t>Education Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52315</t>
+  </si>
+  <si>
+    <t>ILEAD Mentor Supervisor</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52297</t>
+  </si>
+  <si>
+    <t>Chick-fil-A Floor Supervisor</t>
+  </si>
+  <si>
+    <t>Chick Fil A</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52295</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52289</t>
+  </si>
+  <si>
+    <t>Retention Specialist</t>
+  </si>
+  <si>
+    <t>TRiO/Student Support Services</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52279</t>
+  </si>
+  <si>
+    <t>Sociology &amp; Anthropology Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Sociology &amp; Anthropology</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52273</t>
+  </si>
+  <si>
+    <t>Political Science Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Political Science</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52272</t>
+  </si>
+  <si>
+    <t>Student Services Coordinator - ILEAD</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52271</t>
+  </si>
+  <si>
+    <t>Grant Support Coordinator</t>
+  </si>
+  <si>
+    <t>Dean of Letters &amp; Science</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52264</t>
+  </si>
+  <si>
+    <t>Academic Services Coordinator</t>
+  </si>
+  <si>
+    <t>History and Philosophy</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52253</t>
+  </si>
+  <si>
+    <t>Assistant Professor – Instruction and Open Strategies Librarian</t>
+  </si>
+  <si>
+    <t>Library</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52244</t>
+  </si>
+  <si>
+    <t>Administrative Associate III</t>
+  </si>
+  <si>
+    <t>Gallatin College Academic Support</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52222</t>
+  </si>
+  <si>
+    <t>Assistant Banquet Manager</t>
+  </si>
+  <si>
+    <t>University Catering</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52214</t>
+  </si>
+  <si>
+    <t>Pharmacy Technician</t>
+  </si>
+  <si>
+    <t>SWC Pharmacy</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52199</t>
+  </si>
+  <si>
+    <t>Equine NTT Instructor/Assistant Foreman</t>
+  </si>
+  <si>
+    <t>Animal &amp; Range Sciences</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52182</t>
+  </si>
+  <si>
+    <t>Extension Agent - On Farm Irrigation - Flathead Reservation</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52177</t>
+  </si>
+  <si>
+    <t>Program Manager – Local Government Center</t>
+  </si>
+  <si>
+    <t>Extension Local Government Center</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52166</t>
+  </si>
+  <si>
+    <t>Warehouse Worker</t>
+  </si>
+  <si>
+    <t>Miller Dining Commons</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52129</t>
+  </si>
+  <si>
+    <t>Commissary Cook II</t>
+  </si>
+  <si>
+    <t>Salad Productions</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52121</t>
+  </si>
+  <si>
+    <t>HDCH Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52104</t>
+  </si>
+  <si>
+    <t>Custodian I - Full Time (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Auxiliary Services Administration</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52082</t>
+  </si>
+  <si>
+    <t>Assistant to the Director</t>
+  </si>
+  <si>
+    <t>Montana AHEC/Rural Health</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52079</t>
+  </si>
+  <si>
+    <t>Flathead County Agriculture Extension Agent</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52077</t>
+  </si>
+  <si>
+    <t>Indigenous Relations Program Lead</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52069</t>
+  </si>
+  <si>
+    <t>Research Data Engineer</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52049</t>
+  </si>
+  <si>
+    <t>College of Nursing Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Nursing Departments</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52040</t>
+  </si>
+  <si>
+    <t>Associate Director of Accounting/Controller</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52015</t>
+  </si>
+  <si>
+    <t>Assistant Professor of Microbiology</t>
+  </si>
+  <si>
+    <t>Microbiology &amp; Cell Biology</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/52009</t>
+  </si>
+  <si>
+    <t>Academic/Student Success Advisor</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51961</t>
+  </si>
+  <si>
+    <t>Catering Floor Supervisor</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51876</t>
+  </si>
+  <si>
+    <t>Sous Chef</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51827</t>
+  </si>
+  <si>
+    <t>Research Project Assistant</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51821</t>
+  </si>
+  <si>
+    <t>Mathematics, Mathematics Education and Statistics Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Mathematical Sciences</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51817</t>
+  </si>
+  <si>
+    <t>Global Health Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Liberal Studies</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51689</t>
+  </si>
+  <si>
+    <t>Cashier Full-Time (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51680</t>
+  </si>
+  <si>
+    <t>Dishwasher - Full-TIme (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51676</t>
+  </si>
+  <si>
+    <t>Custodian I - PT Pool</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51663</t>
+  </si>
+  <si>
+    <t>Program Director - Interior Design</t>
+  </si>
+  <si>
+    <t>Interior Design</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51646</t>
+  </si>
+  <si>
+    <t>Postdoctoral Researcher – Political Science and Systems Engineering</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51628</t>
+  </si>
+  <si>
+    <t>Department Head &amp; Associate Professor, Accounting &amp; Finance Department</t>
+  </si>
+  <si>
+    <t>Jabs College of Business Instruct</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51556</t>
+  </si>
+  <si>
+    <t>Plant Sciences &amp; Plant Pathology Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Plant Sciences</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51514</t>
+  </si>
+  <si>
+    <t>NAGPRA Program Lead</t>
+  </si>
+  <si>
+    <t>Research Integrity and Compliance</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51504</t>
+  </si>
+  <si>
+    <t>Director of Enterprise Application Support</t>
+  </si>
+  <si>
+    <t>UIT Business Operations</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51437</t>
+  </si>
+  <si>
+    <t>Police Officer Commissioned (non-certified)</t>
+  </si>
+  <si>
+    <t>University Police</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51324</t>
+  </si>
+  <si>
+    <t>Leadership Fellows Non-Tenure Track Faculty</t>
+  </si>
+  <si>
+    <t>Leadership Fellows</t>
+  </si>
+  <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51221</t>
+  </si>
+  <si>
+    <t>Agricultural Economics &amp; Economics Non-Tenure Track Visiting Instructor (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Agricultural Economics &amp; Economics</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51218</t>
+  </si>
+  <si>
+    <t>MSSE Instructor Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/51101</t>
+  </si>
+  <si>
+    <t>History Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/50979</t>
+  </si>
+  <si>
+    <t>Philosophy Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/50977</t>
+  </si>
+  <si>
+    <t>University Studies and College Success Non-Tenure Track Faculty</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/50953</t>
+  </si>
+  <si>
+    <t>Earth Sciences Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>Earth Sciences</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/50897</t>
+  </si>
+  <si>
+    <t>Assistant/Associate/Full Professor - Nursing</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/50826</t>
+  </si>
+  <si>
+    <t>Gen Ed - Humanities Non-Tenure Track Faculty - Gallatin College (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/50726</t>
+  </si>
+  <si>
+    <t>Gen Ed - Natural Sciences Non-Tenure Track Faculty - Gallatin College (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/50725</t>
+  </si>
+  <si>
+    <t>Gen Ed - Social Sciences Non-Tenure Track Faculty - Gallatin College (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/50724</t>
+  </si>
+  <si>
+    <t>Gen Ed - Workforce Non-Tenure Track Faculty - Gallatin College (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/50723</t>
+  </si>
+  <si>
+    <t>Analytics Instructors for the Jake Jabs College of Business &amp; Entrepreneurship Non-Tenure Track Faculty (Applicant Pool)</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>https://jobs.montana.edu/postings/50441</t>
+  </si>
+  <si>
+    <t>Mechanical &amp; Industrial Engineering Non-Tenure Track Faculty (Applicant Pool)</t>
   </si>
   <si>
     <t>Mechanical &amp; Industrial Engineering</t>
   </si>
   <si>
-    <t>https://jobs.montana.edu/postings/52555</t>
-  </si>
-  <si>
-    <t>Registered Dietitian Nutritionist</t>
-  </si>
-  <si>
-    <t>Athletics</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52554</t>
-  </si>
-  <si>
-    <t>Administrative Associate IV, Buffalo Nations</t>
-  </si>
-  <si>
-    <t>Food Systems Nutrition &amp; Kinesiolog</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52548</t>
-  </si>
-  <si>
-    <t>Graphic Designer</t>
-  </si>
-  <si>
-    <t>Museum of the Rockies</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52538</t>
-  </si>
-  <si>
-    <t>Academic Success Coordinator - Gianforte School of Computing</t>
-  </si>
-  <si>
-    <t>Gianforte School of Computing</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52532</t>
-  </si>
-  <si>
-    <t>Budget and Fiscal Manager</t>
-  </si>
-  <si>
-    <t>Graduate School</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52524</t>
-  </si>
-  <si>
-    <t>Academic Advisor II</t>
-  </si>
-  <si>
-    <t>MSSE MS Science Education</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52523</t>
-  </si>
-  <si>
-    <t>Instructional Technology Specialist</t>
-  </si>
-  <si>
-    <t>Center for Faculty Excellence</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52513</t>
-  </si>
-  <si>
-    <t>Mechanic II or III</t>
-  </si>
-  <si>
-    <t>Facility Services</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52507</t>
-  </si>
-  <si>
-    <t>Extension Agent - Fallon County</t>
-  </si>
-  <si>
-    <t>Extension Agents/Field</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Budget and Finance. </t>
-  </si>
-  <si>
-    <t>SWC AVP OPs</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52499</t>
-  </si>
-  <si>
-    <t>Extension Grant and Fiscal Coordinator</t>
-  </si>
-  <si>
-    <t>Administration - MSU Extension</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52498</t>
-  </si>
-  <si>
-    <t>Admissions Specialist</t>
-  </si>
-  <si>
-    <t>Admissions</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52495</t>
-  </si>
-  <si>
-    <t>Executive Director, QCORE</t>
-  </si>
-  <si>
-    <t>Physics</t>
-  </si>
-  <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52484</t>
-  </si>
-  <si>
-    <t>Computer Support Specialist II</t>
-  </si>
-  <si>
-    <t>College of Ag Team</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52483</t>
-  </si>
-  <si>
-    <t>Fire Marshal</t>
-  </si>
-  <si>
-    <t>Safety &amp; Risk Mgmt</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52482</t>
-  </si>
-  <si>
-    <t>Supply and Inventory Associate</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52476</t>
-  </si>
-  <si>
-    <t>Event Coordinator</t>
-  </si>
-  <si>
-    <t>Conference &amp; Event Services</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52471</t>
-  </si>
-  <si>
-    <t>University Studies Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>University Studies</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52467</t>
-  </si>
-  <si>
-    <t>Equipment Operator II</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52460</t>
-  </si>
-  <si>
-    <t>Turtle Island Tales Program Coordinator I</t>
-  </si>
-  <si>
-    <t>American Indian Rural Health Equity</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52453</t>
-  </si>
-  <si>
-    <t>Training and Development Specialist</t>
-  </si>
-  <si>
-    <t>DISC</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52451</t>
-  </si>
-  <si>
-    <t>Research Assistant III *Miles City-Fort Keogh*</t>
-  </si>
-  <si>
-    <t>AES LARRS</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52450</t>
-  </si>
-  <si>
-    <t>Senior Technology Manager</t>
-  </si>
-  <si>
-    <t>MSU Technology Transfer Office</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52448</t>
-  </si>
-  <si>
-    <t>Program Coordinator, Ivan Doig Center for the Study of the Lands &amp; Peoples of the North American West</t>
-  </si>
-  <si>
-    <t>Western Lands &amp; People Center</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52446</t>
-  </si>
-  <si>
-    <t>Assistant Director - Testing Services</t>
-  </si>
-  <si>
-    <t>University Testing Services</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52444</t>
-  </si>
-  <si>
-    <t>FLEX Academic Advisors - (Pooled Positions)</t>
-  </si>
-  <si>
-    <t>Advising Commons</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52443</t>
-  </si>
-  <si>
-    <t>Faculty Instructor &amp; Bracken Business Center Coach for the Jake Jabs College of Business &amp; Entrepreneurship Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Jabs Program Fee</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52440</t>
-  </si>
-  <si>
-    <t>Chief Marketing Officer</t>
-  </si>
-  <si>
-    <t>University Communications</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52438</t>
-  </si>
-  <si>
-    <t>Admissions Evaluator</t>
-  </si>
-  <si>
-    <t>2026-07-30</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52435</t>
-  </si>
-  <si>
-    <t>Gen Ed – Health Sciences Non-Tenure Track Faculty – Gallatin College (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Gallatin College</t>
-  </si>
-  <si>
-    <t>2026-07-29</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52430</t>
-  </si>
-  <si>
-    <t>Cook II (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Culinary Services Administration</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52423</t>
-  </si>
-  <si>
-    <t>Custodian II - Housing</t>
-  </si>
-  <si>
-    <t>Residence Life Administration</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52416</t>
-  </si>
-  <si>
-    <t>Career Education Coach</t>
-  </si>
-  <si>
-    <t>Career Services</t>
-  </si>
-  <si>
-    <t>2026-07-28</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52413</t>
-  </si>
-  <si>
-    <t>Data Systems Manager</t>
-  </si>
-  <si>
-    <t>UIT Enterprise Services Group CUF</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52411</t>
-  </si>
-  <si>
-    <t>Grants and Fiscal Manager</t>
-  </si>
-  <si>
-    <t>Western Transportation Institute</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52409</t>
-  </si>
-  <si>
-    <t>Extension Agent – Agriculture and 4-H Youth Development – Pondera County</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52408</t>
-  </si>
-  <si>
-    <t>Extension Agent – Family and Consumer Sciences and 4-H Youth Development – Pondera County</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52407</t>
-  </si>
-  <si>
-    <t>Operator-In-Training</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52406</t>
-  </si>
-  <si>
-    <t>Academic Advisor I or II</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52404</t>
-  </si>
-  <si>
-    <t>Cook III (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52389</t>
-  </si>
-  <si>
-    <t>Budget and Fiscal Director</t>
-  </si>
-  <si>
-    <t>Dean Educ/HHD</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52369</t>
-  </si>
-  <si>
-    <t>Assistant Professor, Cropping System Agronomist *Havre, MT*</t>
-  </si>
-  <si>
-    <t>AES NARC</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52366</t>
-  </si>
-  <si>
-    <t>Software Engineer</t>
-  </si>
-  <si>
-    <t>2026-07-22</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52345</t>
-  </si>
-  <si>
-    <t>Computer Supp Spec II</t>
-  </si>
-  <si>
-    <t>College of L&amp;S Team</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52344</t>
-  </si>
-  <si>
-    <t>Floor Supervisor - Dining Halls</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52339</t>
-  </si>
-  <si>
-    <t>Early Childhood Classroom Support</t>
-  </si>
-  <si>
-    <t>Human Development &amp;Community Health</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52332</t>
-  </si>
-  <si>
-    <t>Research Associate/Research Scientist/Research Engineer</t>
-  </si>
-  <si>
-    <t>Spectrum Lab</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52331</t>
-  </si>
-  <si>
-    <t>Strategic Partnerships and Industry Relations Lead</t>
-  </si>
-  <si>
-    <t>2026-07-21</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52326</t>
-  </si>
-  <si>
-    <t>Financial Associate</t>
-  </si>
-  <si>
-    <t>Fiscal Shared Services</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52323</t>
-  </si>
-  <si>
-    <t>Instructor of Architecture Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Architecture</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52318</t>
-  </si>
-  <si>
-    <t>Visiting Scholar - Architecture (Non-Tenure Track Faculty Applicant Pool)</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52317</t>
-  </si>
-  <si>
-    <t>Education Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52315</t>
-  </si>
-  <si>
-    <t>ILEAD Mentor Supervisor</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52297</t>
-  </si>
-  <si>
-    <t>Chick-fil-A Floor Supervisor</t>
-  </si>
-  <si>
-    <t>Chick Fil A</t>
-  </si>
-  <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52295</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52289</t>
-  </si>
-  <si>
-    <t>Retention Specialist</t>
-  </si>
-  <si>
-    <t>TRiO/Student Support Services</t>
-  </si>
-  <si>
-    <t>2026-07-17</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52279</t>
-  </si>
-  <si>
-    <t>Sociology &amp; Anthropology Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Sociology &amp; Anthropology</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52273</t>
-  </si>
-  <si>
-    <t>Political Science Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Political Science</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52272</t>
-  </si>
-  <si>
-    <t>Student Services Coordinator - ILEAD</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52271</t>
-  </si>
-  <si>
-    <t>Grant Support Coordinator</t>
-  </si>
-  <si>
-    <t>Dean of Letters &amp; Science</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52264</t>
-  </si>
-  <si>
-    <t>Academic Services Coordinator</t>
-  </si>
-  <si>
-    <t>History and Philosophy</t>
-  </si>
-  <si>
-    <t>2026-07-15</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52253</t>
-  </si>
-  <si>
-    <t>Assistant Professor – Instruction and Open Strategies Librarian</t>
-  </si>
-  <si>
-    <t>Library</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52244</t>
-  </si>
-  <si>
-    <t>Administrative Associate III</t>
-  </si>
-  <si>
-    <t>Gallatin College Academic Support</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52222</t>
-  </si>
-  <si>
-    <t>Assistant Banquet Manager</t>
-  </si>
-  <si>
-    <t>University Catering</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52214</t>
-  </si>
-  <si>
-    <t>Pharmacy Technician</t>
-  </si>
-  <si>
-    <t>SWC Pharmacy</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52199</t>
-  </si>
-  <si>
-    <t>Equine NTT Instructor/Assistant Foreman</t>
-  </si>
-  <si>
-    <t>Animal &amp; Range Sciences</t>
-  </si>
-  <si>
-    <t>2026-07-09</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52182</t>
-  </si>
-  <si>
-    <t>Extension Agent - On Farm Irrigation - Flathead Reservation</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52177</t>
-  </si>
-  <si>
-    <t>Program Manager – Local Government Center</t>
-  </si>
-  <si>
-    <t>Extension Local Government Center</t>
-  </si>
-  <si>
-    <t>2026-07-08</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52166</t>
-  </si>
-  <si>
-    <t>Warehouse Worker</t>
-  </si>
-  <si>
-    <t>Miller Dining Commons</t>
-  </si>
-  <si>
-    <t>2026-07-07</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52129</t>
-  </si>
-  <si>
-    <t>Commissary Cook II</t>
-  </si>
-  <si>
-    <t>Salad Productions</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52121</t>
-  </si>
-  <si>
-    <t>HDCH Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52104</t>
-  </si>
-  <si>
-    <t>Custodian I - Full Time (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Auxiliary Services Administration</t>
-  </si>
-  <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52082</t>
-  </si>
-  <si>
-    <t>Assistant to the Director</t>
-  </si>
-  <si>
-    <t>Montana AHEC/Rural Health</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52079</t>
-  </si>
-  <si>
-    <t>Flathead County Agriculture Extension Agent</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52077</t>
-  </si>
-  <si>
-    <t>Indigenous Relations Program Lead</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52069</t>
-  </si>
-  <si>
-    <t>Research Data Engineer</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52049</t>
-  </si>
-  <si>
-    <t>College of Nursing Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Nursing Departments</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52040</t>
-  </si>
-  <si>
-    <t>Associate Director of Accounting/Controller</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52015</t>
-  </si>
-  <si>
-    <t>Assistant Professor of Microbiology</t>
-  </si>
-  <si>
-    <t>Microbiology &amp; Cell Biology</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/52009</t>
-  </si>
-  <si>
-    <t>Academic/Student Success Advisor</t>
-  </si>
-  <si>
-    <t>2026-06-22</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51961</t>
-  </si>
-  <si>
-    <t>Catering Floor Supervisor</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51876</t>
-  </si>
-  <si>
-    <t>Sous Chef</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51827</t>
-  </si>
-  <si>
-    <t>Research Project Assistant</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51821</t>
-  </si>
-  <si>
-    <t>Mathematics, Mathematics Education and Statistics Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Mathematical Sciences</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51817</t>
-  </si>
-  <si>
-    <t>Global Health Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Liberal Studies</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51689</t>
-  </si>
-  <si>
-    <t>Cashier Full-Time (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51680</t>
-  </si>
-  <si>
-    <t>Dishwasher - Full-TIme (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51676</t>
-  </si>
-  <si>
-    <t>Custodian I - PT Pool</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51663</t>
-  </si>
-  <si>
-    <t>Program Director - Interior Design</t>
-  </si>
-  <si>
-    <t>Interior Design</t>
-  </si>
-  <si>
-    <t>2026-05-27</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51646</t>
-  </si>
-  <si>
-    <t>Postdoctoral Researcher – Political Science and Systems Engineering</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51628</t>
-  </si>
-  <si>
-    <t>Department Head &amp; Associate Professor, Accounting &amp; Finance Department</t>
-  </si>
-  <si>
-    <t>Jabs College of Business Instruct</t>
-  </si>
-  <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51556</t>
-  </si>
-  <si>
-    <t>Plant Sciences &amp; Plant Pathology Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Plant Sciences</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51514</t>
-  </si>
-  <si>
-    <t>NAGPRA Program Lead</t>
-  </si>
-  <si>
-    <t>Research Integrity and Compliance</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51504</t>
-  </si>
-  <si>
-    <t>Director of Enterprise Application Support</t>
-  </si>
-  <si>
-    <t>UIT Business Operations</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51437</t>
-  </si>
-  <si>
-    <t>Police Officer Commissioned (non-certified)</t>
-  </si>
-  <si>
-    <t>University Police</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51324</t>
-  </si>
-  <si>
-    <t>Leadership Fellows Non-Tenure Track Faculty</t>
-  </si>
-  <si>
-    <t>Leadership Fellows</t>
-  </si>
-  <si>
-    <t>2026-04-22</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51221</t>
-  </si>
-  <si>
-    <t>Agricultural Economics &amp; Economics Non-Tenure Track Visiting Instructor (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Agricultural Economics &amp; Economics</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51218</t>
-  </si>
-  <si>
-    <t>MSSE Instructor Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/51101</t>
-  </si>
-  <si>
-    <t>History Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/50979</t>
-  </si>
-  <si>
-    <t>Philosophy Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/50977</t>
-  </si>
-  <si>
-    <t>University Studies and College Success Non-Tenure Track Faculty</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/50953</t>
-  </si>
-  <si>
-    <t>Earth Sciences Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>Earth Sciences</t>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/50897</t>
-  </si>
-  <si>
-    <t>Assistant/Associate/Full Professor - Nursing</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/50826</t>
-  </si>
-  <si>
-    <t>Gen Ed - Humanities Non-Tenure Track Faculty - Gallatin College (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>2026-03-13</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/50726</t>
-  </si>
-  <si>
-    <t>Gen Ed - Natural Sciences Non-Tenure Track Faculty - Gallatin College (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/50725</t>
-  </si>
-  <si>
-    <t>Gen Ed - Social Sciences Non-Tenure Track Faculty - Gallatin College (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/50724</t>
-  </si>
-  <si>
-    <t>Gen Ed - Workforce Non-Tenure Track Faculty - Gallatin College (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/50723</t>
-  </si>
-  <si>
-    <t>Analytics Instructors for the Jake Jabs College of Business &amp; Entrepreneurship Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
-  </si>
-  <si>
-    <t>https://jobs.montana.edu/postings/50441</t>
-  </si>
-  <si>
-    <t>Mechanical &amp; Industrial Engineering Non-Tenure Track Faculty (Applicant Pool)</t>
-  </si>
-  <si>
     <t>2026-02-02</t>
   </si>
   <si>
@@ -1981,13 +1975,19 @@
     <t>https://montanatechuniversity.applytojob.com/apply/K7MU7DFEew/Visiting-Lab-InstructorLab-DirectorEnvironmental-Engineering</t>
   </si>
   <si>
+    <t>Instructional Specialist, Foundational Math</t>
+  </si>
+  <si>
+    <t>KALISPELL, MT 59901</t>
+  </si>
+  <si>
+    <t>Flathead Valley Community College</t>
+  </si>
+  <si>
+    <t>https://www.paycomonline.net/v4/ats/web.php/portal/23D9610C7FF62DF6DF80223B0B1ED6E3/jobs/75762</t>
+  </si>
+  <si>
     <t>Adjunct Instructor, Music</t>
-  </si>
-  <si>
-    <t>KALISPELL, MT 59901</t>
-  </si>
-  <si>
-    <t>Flathead Valley Community College</t>
   </si>
   <si>
     <t>https://www.paycomonline.net/v4/ats/web.php/portal/23D9610C7FF62DF6DF80223B0B1ED6E3/jobs/75716</t>
@@ -3290,13 +3290,13 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1">
         <v>46245</v>
@@ -3304,13 +3304,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
@@ -3330,7 +3330,7 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
@@ -3350,13 +3350,13 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" s="1">
         <v>46245</v>
@@ -3364,13 +3364,13 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
@@ -3390,13 +3390,13 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1">
         <v>46245</v>
@@ -3404,13 +3404,13 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
@@ -3430,7 +3430,7 @@
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
@@ -3450,13 +3450,13 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F12" s="1">
         <v>46245</v>
@@ -3464,13 +3464,13 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
@@ -3490,7 +3490,7 @@
         <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
@@ -3510,13 +3510,13 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F15" s="1">
         <v>46245</v>
@@ -3524,13 +3524,13 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
@@ -3550,7 +3550,7 @@
         <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
@@ -3567,16 +3567,16 @@
         <v>61</v>
       </c>
       <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s">
         <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s">
-        <v>63</v>
       </c>
       <c r="F18" s="1">
         <v>46245</v>
@@ -3584,13 +3584,13 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s">
         <v>64</v>
       </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
         <v>9</v>
@@ -3610,7 +3610,7 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
@@ -3627,10 +3627,10 @@
         <v>69</v>
       </c>
       <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
         <v>70</v>
-      </c>
-      <c r="C21" t="s">
-        <v>56</v>
       </c>
       <c r="D21" t="s">
         <v>9</v>
@@ -3647,10 +3647,10 @@
         <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
         <v>9</v>
@@ -3670,7 +3670,7 @@
         <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
@@ -3690,7 +3690,7 @@
         <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
@@ -3710,7 +3710,7 @@
         <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
@@ -3730,13 +3730,13 @@
         <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F26" s="1">
         <v>46245</v>
@@ -3744,13 +3744,13 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
         <v>9</v>
@@ -3770,7 +3770,7 @@
         <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
         <v>9</v>
@@ -3790,7 +3790,7 @@
         <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
         <v>9</v>
@@ -3810,7 +3810,7 @@
         <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
@@ -3827,10 +3827,10 @@
         <v>100</v>
       </c>
       <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" t="s">
         <v>101</v>
-      </c>
-      <c r="C31" t="s">
-        <v>89</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
@@ -3847,16 +3847,16 @@
         <v>103</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F32" s="1">
         <v>46245</v>
@@ -3864,13 +3864,13 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
@@ -3890,7 +3890,7 @@
         <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
@@ -3910,13 +3910,13 @@
         <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F35" s="1">
         <v>46245</v>
@@ -3924,13 +3924,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
@@ -3950,7 +3950,7 @@
         <v>121</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
@@ -3967,16 +3967,16 @@
         <v>123</v>
       </c>
       <c r="B38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" t="s">
+        <v>115</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" t="s">
         <v>124</v>
-      </c>
-      <c r="C38" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" t="s">
-        <v>125</v>
       </c>
       <c r="F38" s="1">
         <v>46245</v>
@@ -3984,19 +3984,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
+        <v>125</v>
+      </c>
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" t="s">
         <v>126</v>
-      </c>
-      <c r="B39" t="s">
-        <v>42</v>
-      </c>
-      <c r="C39" t="s">
-        <v>118</v>
-      </c>
-      <c r="D39" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" t="s">
-        <v>127</v>
       </c>
       <c r="F39" s="1">
         <v>46245</v>
@@ -4004,19 +4004,19 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" t="s">
         <v>128</v>
-      </c>
-      <c r="B40" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" t="s">
-        <v>129</v>
       </c>
       <c r="F40" s="1">
         <v>46245</v>
@@ -4024,19 +4024,19 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
+        <v>115</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" t="s">
         <v>130</v>
-      </c>
-      <c r="B41" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" t="s">
-        <v>131</v>
       </c>
       <c r="F41" s="1">
         <v>46245</v>
@@ -4044,13 +4044,13 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" t="s">
         <v>132</v>
-      </c>
-      <c r="B42" t="s">
-        <v>95</v>
-      </c>
-      <c r="C42" t="s">
-        <v>118</v>
       </c>
       <c r="D42" t="s">
         <v>9</v>
@@ -4067,16 +4067,16 @@
         <v>134</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D43" t="s">
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F43" s="1">
         <v>46245</v>
@@ -4084,13 +4084,13 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D44" t="s">
         <v>9</v>
@@ -4107,10 +4107,10 @@
         <v>141</v>
       </c>
       <c r="B45" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45" t="s">
         <v>142</v>
-      </c>
-      <c r="C45" t="s">
-        <v>139</v>
       </c>
       <c r="D45" t="s">
         <v>9</v>
@@ -4127,10 +4127,10 @@
         <v>144</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="C46" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D46" t="s">
         <v>9</v>
@@ -4147,16 +4147,16 @@
         <v>147</v>
       </c>
       <c r="B47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" t="s">
+        <v>142</v>
+      </c>
+      <c r="D47" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" t="s">
         <v>148</v>
-      </c>
-      <c r="C47" t="s">
-        <v>145</v>
-      </c>
-      <c r="D47" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" t="s">
-        <v>149</v>
       </c>
       <c r="F47" s="1">
         <v>46245</v>
@@ -4164,13 +4164,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" t="s">
         <v>150</v>
       </c>
-      <c r="B48" t="s">
-        <v>111</v>
-      </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D48" t="s">
         <v>9</v>
@@ -4190,7 +4190,7 @@
         <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D49" t="s">
         <v>9</v>
@@ -4207,10 +4207,10 @@
         <v>155</v>
       </c>
       <c r="B50" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" t="s">
         <v>156</v>
-      </c>
-      <c r="C50" t="s">
-        <v>145</v>
       </c>
       <c r="D50" t="s">
         <v>9</v>
@@ -4227,10 +4227,10 @@
         <v>158</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="C51" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D51" t="s">
         <v>9</v>
@@ -4250,7 +4250,7 @@
         <v>162</v>
       </c>
       <c r="C52" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D52" t="s">
         <v>9</v>
@@ -4267,16 +4267,16 @@
         <v>164</v>
       </c>
       <c r="B53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C53" t="s">
+        <v>156</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" t="s">
         <v>165</v>
-      </c>
-      <c r="C53" t="s">
-        <v>159</v>
-      </c>
-      <c r="D53" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" t="s">
-        <v>166</v>
       </c>
       <c r="F53" s="1">
         <v>46245</v>
@@ -4284,13 +4284,13 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" t="s">
         <v>167</v>
       </c>
-      <c r="B54" t="s">
-        <v>165</v>
-      </c>
       <c r="C54" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D54" t="s">
         <v>9</v>
@@ -4307,16 +4307,16 @@
         <v>169</v>
       </c>
       <c r="B55" t="s">
+        <v>167</v>
+      </c>
+      <c r="C55" t="s">
+        <v>156</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
         <v>170</v>
-      </c>
-      <c r="C55" t="s">
-        <v>159</v>
-      </c>
-      <c r="D55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" t="s">
-        <v>171</v>
       </c>
       <c r="F55" s="1">
         <v>46245</v>
@@ -4324,19 +4324,19 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
+        <v>171</v>
+      </c>
+      <c r="B56" t="s">
         <v>172</v>
       </c>
-      <c r="B56" t="s">
-        <v>170</v>
-      </c>
       <c r="C56" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D56" t="s">
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F56" s="1">
         <v>46245</v>
@@ -4344,19 +4344,19 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="B57" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" t="s">
+        <v>173</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" t="s">
         <v>175</v>
-      </c>
-      <c r="C57" t="s">
-        <v>176</v>
-      </c>
-      <c r="D57" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" t="s">
-        <v>177</v>
       </c>
       <c r="F57" s="1">
         <v>46245</v>
@@ -4364,19 +4364,19 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="C58" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D58" t="s">
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F58" s="1">
         <v>46245</v>
@@ -4384,19 +4384,19 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B59" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C59" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D59" t="s">
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F59" s="1">
         <v>46245</v>
@@ -4404,13 +4404,13 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B60" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C60" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D60" t="s">
         <v>9</v>
@@ -4427,16 +4427,16 @@
         <v>187</v>
       </c>
       <c r="B61" t="s">
+        <v>167</v>
+      </c>
+      <c r="C61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" t="s">
         <v>188</v>
-      </c>
-      <c r="C61" t="s">
-        <v>185</v>
-      </c>
-      <c r="D61" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" t="s">
-        <v>189</v>
       </c>
       <c r="F61" s="1">
         <v>46245</v>
@@ -4444,13 +4444,13 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
+        <v>189</v>
+      </c>
+      <c r="B62" t="s">
         <v>190</v>
       </c>
-      <c r="B62" t="s">
-        <v>170</v>
-      </c>
       <c r="C62" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D62" t="s">
         <v>9</v>
@@ -4470,13 +4470,13 @@
         <v>193</v>
       </c>
       <c r="C63" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D63" t="s">
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F63" s="1">
         <v>46245</v>
@@ -4484,13 +4484,13 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B64" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C64" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D64" t="s">
         <v>9</v>
@@ -4510,13 +4510,13 @@
         <v>200</v>
       </c>
       <c r="C65" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D65" t="s">
         <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F65" s="1">
         <v>46245</v>
@@ -4524,13 +4524,13 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B66" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C66" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D66" t="s">
         <v>9</v>
@@ -4550,13 +4550,13 @@
         <v>207</v>
       </c>
       <c r="C67" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D67" t="s">
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F67" s="1">
         <v>46245</v>
@@ -4564,19 +4564,19 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B68" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C68" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F68" s="1">
         <v>46245</v>
@@ -4584,19 +4584,19 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B69" t="s">
-        <v>214</v>
+        <v>39</v>
       </c>
       <c r="C69" t="s">
+        <v>212</v>
+      </c>
+      <c r="D69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" t="s">
         <v>215</v>
-      </c>
-      <c r="D69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" t="s">
-        <v>216</v>
       </c>
       <c r="F69" s="1">
         <v>46245</v>
@@ -4604,19 +4604,19 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
+        <v>216</v>
+      </c>
+      <c r="B70" t="s">
         <v>217</v>
       </c>
-      <c r="B70" t="s">
-        <v>42</v>
-      </c>
       <c r="C70" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F70" s="1">
         <v>46245</v>
@@ -4624,19 +4624,19 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C71" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D71" t="s">
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F71" s="1">
         <v>46245</v>
@@ -4644,13 +4644,13 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B72" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C72" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D72" t="s">
         <v>9</v>
@@ -4667,10 +4667,10 @@
         <v>227</v>
       </c>
       <c r="B73" t="s">
+        <v>150</v>
+      </c>
+      <c r="C73" t="s">
         <v>228</v>
-      </c>
-      <c r="C73" t="s">
-        <v>225</v>
       </c>
       <c r="D73" t="s">
         <v>9</v>
@@ -4687,16 +4687,16 @@
         <v>230</v>
       </c>
       <c r="B74" t="s">
-        <v>153</v>
+        <v>231</v>
       </c>
       <c r="C74" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D74" t="s">
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F74" s="1">
         <v>46245</v>
@@ -4704,13 +4704,13 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B75" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C75" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D75" t="s">
         <v>9</v>
@@ -4727,16 +4727,16 @@
         <v>237</v>
       </c>
       <c r="B76" t="s">
+        <v>39</v>
+      </c>
+      <c r="C76" t="s">
+        <v>232</v>
+      </c>
+      <c r="D76" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" t="s">
         <v>238</v>
-      </c>
-      <c r="C76" t="s">
-        <v>235</v>
-      </c>
-      <c r="D76" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" t="s">
-        <v>239</v>
       </c>
       <c r="F76" s="1">
         <v>46245</v>
@@ -4744,13 +4744,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
+        <v>239</v>
+      </c>
+      <c r="B77" t="s">
+        <v>19</v>
+      </c>
+      <c r="C77" t="s">
         <v>240</v>
-      </c>
-      <c r="B77" t="s">
-        <v>42</v>
-      </c>
-      <c r="C77" t="s">
-        <v>235</v>
       </c>
       <c r="D77" t="s">
         <v>9</v>
@@ -4770,13 +4770,13 @@
         <v>22</v>
       </c>
       <c r="C78" t="s">
+        <v>240</v>
+      </c>
+      <c r="D78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" t="s">
         <v>243</v>
-      </c>
-      <c r="D78" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" t="s">
-        <v>244</v>
       </c>
       <c r="F78" s="1">
         <v>46245</v>
@@ -4784,19 +4784,19 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
+        <v>244</v>
+      </c>
+      <c r="B79" t="s">
         <v>245</v>
       </c>
-      <c r="B79" t="s">
-        <v>25</v>
-      </c>
       <c r="C79" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D79" t="s">
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F79" s="1">
         <v>46245</v>
@@ -4804,10 +4804,10 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B80" t="s">
-        <v>248</v>
+        <v>19</v>
       </c>
       <c r="C80" t="s">
         <v>249</v>
@@ -4827,16 +4827,16 @@
         <v>251</v>
       </c>
       <c r="B81" t="s">
-        <v>22</v>
+        <v>252</v>
       </c>
       <c r="C81" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D81" t="s">
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F81" s="1">
         <v>46245</v>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B82" t="s">
-        <v>255</v>
+        <v>104</v>
       </c>
       <c r="C82" t="s">
         <v>256</v>
@@ -4867,7 +4867,7 @@
         <v>258</v>
       </c>
       <c r="B83" t="s">
-        <v>107</v>
+        <v>204</v>
       </c>
       <c r="C83" t="s">
         <v>259</v>
@@ -4887,7 +4887,7 @@
         <v>261</v>
       </c>
       <c r="B84" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C84" t="s">
         <v>262</v>
@@ -4907,16 +4907,16 @@
         <v>264</v>
       </c>
       <c r="B85" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C85" t="s">
+        <v>262</v>
+      </c>
+      <c r="D85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" t="s">
         <v>265</v>
-      </c>
-      <c r="D85" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" t="s">
-        <v>266</v>
       </c>
       <c r="F85" s="1">
         <v>46245</v>
@@ -4924,13 +4924,13 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
+        <v>266</v>
+      </c>
+      <c r="B86" t="s">
         <v>267</v>
       </c>
-      <c r="B86" t="s">
-        <v>214</v>
-      </c>
       <c r="C86" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
         <v>9</v>
@@ -4950,13 +4950,13 @@
         <v>270</v>
       </c>
       <c r="C87" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D87" t="s">
         <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F87" s="1">
         <v>46245</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B88" t="s">
-        <v>273</v>
+        <v>108</v>
       </c>
       <c r="C88" t="s">
         <v>274</v>
@@ -4987,16 +4987,16 @@
         <v>276</v>
       </c>
       <c r="B89" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C89" t="s">
+        <v>274</v>
+      </c>
+      <c r="D89" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" t="s">
         <v>277</v>
-      </c>
-      <c r="D89" t="s">
-        <v>9</v>
-      </c>
-      <c r="E89" t="s">
-        <v>278</v>
       </c>
       <c r="F89" s="1">
         <v>46245</v>
@@ -5004,13 +5004,13 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B90" t="s">
         <v>111</v>
       </c>
       <c r="C90" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D90" t="s">
         <v>9</v>
@@ -5027,16 +5027,16 @@
         <v>281</v>
       </c>
       <c r="B91" t="s">
-        <v>114</v>
+        <v>282</v>
       </c>
       <c r="C91" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D91" t="s">
         <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F91" s="1">
         <v>46245</v>
@@ -5044,10 +5044,10 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B92" t="s">
-        <v>285</v>
+        <v>185</v>
       </c>
       <c r="C92" t="s">
         <v>286</v>
@@ -5067,16 +5067,16 @@
         <v>288</v>
       </c>
       <c r="B93" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="C93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D93" t="s">
         <v>9</v>
       </c>
       <c r="E93" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F93" s="1">
         <v>46245</v>
@@ -5084,19 +5084,19 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B94" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C94" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D94" t="s">
         <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F94" s="1">
         <v>46245</v>
@@ -5104,19 +5104,19 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D95" t="s">
         <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F95" s="1">
         <v>46245</v>
@@ -5124,19 +5124,19 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B96" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C96" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D96" t="s">
         <v>9</v>
       </c>
       <c r="E96" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F96" s="1">
         <v>46245</v>
@@ -5144,19 +5144,19 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B97" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C97" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F97" s="1">
         <v>46245</v>
@@ -5164,19 +5164,19 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B98" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C98" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D98" t="s">
         <v>9</v>
       </c>
       <c r="E98" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F98" s="1">
         <v>46245</v>
@@ -5184,13 +5184,13 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B99" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C99" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
@@ -5207,10 +5207,10 @@
         <v>315</v>
       </c>
       <c r="B100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" t="s">
         <v>316</v>
-      </c>
-      <c r="C100" t="s">
-        <v>313</v>
       </c>
       <c r="D100" t="s">
         <v>9</v>
@@ -5227,7 +5227,7 @@
         <v>318</v>
       </c>
       <c r="B101" t="s">
-        <v>32</v>
+        <v>193</v>
       </c>
       <c r="C101" t="s">
         <v>319</v>
@@ -5247,16 +5247,16 @@
         <v>321</v>
       </c>
       <c r="B102" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C102" t="s">
+        <v>319</v>
+      </c>
+      <c r="D102" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" t="s">
         <v>322</v>
-      </c>
-      <c r="D102" t="s">
-        <v>9</v>
-      </c>
-      <c r="E102" t="s">
-        <v>323</v>
       </c>
       <c r="F102" s="1">
         <v>46245</v>
@@ -5264,13 +5264,13 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
+        <v>323</v>
+      </c>
+      <c r="B103" t="s">
+        <v>67</v>
+      </c>
+      <c r="C103" t="s">
         <v>324</v>
-      </c>
-      <c r="B103" t="s">
-        <v>196</v>
-      </c>
-      <c r="C103" t="s">
-        <v>322</v>
       </c>
       <c r="D103" t="s">
         <v>9</v>
@@ -5287,16 +5287,16 @@
         <v>326</v>
       </c>
       <c r="B104" t="s">
-        <v>70</v>
+        <v>327</v>
       </c>
       <c r="C104" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D104" t="s">
         <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F104" s="1">
         <v>46245</v>
@@ -5304,10 +5304,10 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B105" t="s">
-        <v>330</v>
+        <v>245</v>
       </c>
       <c r="C105" t="s">
         <v>331</v>
@@ -5327,7 +5327,7 @@
         <v>333</v>
       </c>
       <c r="B106" t="s">
-        <v>248</v>
+        <v>104</v>
       </c>
       <c r="C106" t="s">
         <v>334</v>
@@ -5347,16 +5347,16 @@
         <v>336</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C107" t="s">
+        <v>334</v>
+      </c>
+      <c r="D107" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" t="s">
         <v>337</v>
-      </c>
-      <c r="D107" t="s">
-        <v>9</v>
-      </c>
-      <c r="E107" t="s">
-        <v>338</v>
       </c>
       <c r="F107" s="1">
         <v>46245</v>
@@ -5364,19 +5364,19 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
+        <v>338</v>
+      </c>
+      <c r="B108" t="s">
+        <v>104</v>
+      </c>
+      <c r="C108" t="s">
+        <v>334</v>
+      </c>
+      <c r="D108" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" t="s">
         <v>339</v>
-      </c>
-      <c r="B108" t="s">
-        <v>107</v>
-      </c>
-      <c r="C108" t="s">
-        <v>337</v>
-      </c>
-      <c r="D108" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" t="s">
-        <v>340</v>
       </c>
       <c r="F108" s="1">
         <v>46245</v>
@@ -5384,19 +5384,19 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
+        <v>340</v>
+      </c>
+      <c r="B109" t="s">
+        <v>104</v>
+      </c>
+      <c r="C109" t="s">
+        <v>334</v>
+      </c>
+      <c r="D109" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" t="s">
         <v>341</v>
-      </c>
-      <c r="B109" t="s">
-        <v>107</v>
-      </c>
-      <c r="C109" t="s">
-        <v>337</v>
-      </c>
-      <c r="D109" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109" t="s">
-        <v>342</v>
       </c>
       <c r="F109" s="1">
         <v>46245</v>
@@ -5404,13 +5404,13 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
+        <v>342</v>
+      </c>
+      <c r="B110" t="s">
+        <v>289</v>
+      </c>
+      <c r="C110" t="s">
         <v>343</v>
-      </c>
-      <c r="B110" t="s">
-        <v>107</v>
-      </c>
-      <c r="C110" t="s">
-        <v>337</v>
       </c>
       <c r="D110" t="s">
         <v>9</v>
@@ -5427,16 +5427,16 @@
         <v>345</v>
       </c>
       <c r="B111" t="s">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="C111" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D111" t="s">
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F111" s="1">
         <v>46245</v>
@@ -5444,19 +5444,19 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="C112" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D112" t="s">
         <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F112" s="1">
         <v>46245</v>
@@ -5464,19 +5464,19 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B113" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C113" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D113" t="s">
         <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F113" s="1">
         <v>46245</v>
@@ -5484,19 +5484,19 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B114" t="s">
-        <v>70</v>
+        <v>289</v>
       </c>
       <c r="C114" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D114" t="s">
         <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F114" s="1">
         <v>46245</v>
@@ -5504,13 +5504,13 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B115" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C115" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D115" t="s">
         <v>9</v>
@@ -5527,10 +5527,10 @@
         <v>360</v>
       </c>
       <c r="B116" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C116" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D116" t="s">
         <v>9</v>
@@ -5547,16 +5547,16 @@
         <v>362</v>
       </c>
       <c r="B117" t="s">
-        <v>292</v>
+        <v>363</v>
       </c>
       <c r="C117" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D117" t="s">
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F117" s="1">
         <v>46245</v>
@@ -5564,13 +5564,13 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
+        <v>366</v>
+      </c>
+      <c r="B118" t="s">
+        <v>252</v>
+      </c>
+      <c r="C118" t="s">
         <v>364</v>
-      </c>
-      <c r="B118" t="s">
-        <v>365</v>
-      </c>
-      <c r="C118" t="s">
-        <v>366</v>
       </c>
       <c r="D118" t="s">
         <v>9</v>
@@ -5587,16 +5587,16 @@
         <v>368</v>
       </c>
       <c r="B119" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C119" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D119" t="s">
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F119" s="1">
         <v>46245</v>
@@ -5604,19 +5604,19 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B120" t="s">
-        <v>255</v>
+        <v>372</v>
       </c>
       <c r="C120" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D120" t="s">
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F120" s="1">
         <v>46245</v>
@@ -5624,19 +5624,19 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B121" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C121" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D121" t="s">
         <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F121" s="1">
         <v>46245</v>
@@ -5644,13 +5644,13 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B122" t="s">
-        <v>377</v>
+        <v>270</v>
       </c>
       <c r="C122" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D122" t="s">
         <v>9</v>
@@ -5667,16 +5667,16 @@
         <v>379</v>
       </c>
       <c r="B123" t="s">
-        <v>273</v>
+        <v>380</v>
       </c>
       <c r="C123" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D123" t="s">
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F123" s="1">
         <v>46245</v>
@@ -5684,13 +5684,13 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B124" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C124" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D124" t="s">
         <v>9</v>
@@ -5707,10 +5707,10 @@
         <v>384</v>
       </c>
       <c r="B125" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C125" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
@@ -5727,10 +5727,10 @@
         <v>386</v>
       </c>
       <c r="B126" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C126" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D126" t="s">
         <v>9</v>
@@ -5747,10 +5747,10 @@
         <v>388</v>
       </c>
       <c r="B127" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C127" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D127" t="s">
         <v>9</v>
@@ -5767,10 +5767,10 @@
         <v>390</v>
       </c>
       <c r="B128" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C128" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D128" t="s">
         <v>9</v>
@@ -5787,10 +5787,10 @@
         <v>392</v>
       </c>
       <c r="B129" t="s">
-        <v>382</v>
+        <v>52</v>
       </c>
       <c r="C129" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D129" t="s">
         <v>9</v>
@@ -5807,16 +5807,16 @@
         <v>394</v>
       </c>
       <c r="B130" t="s">
-        <v>55</v>
+        <v>395</v>
       </c>
       <c r="C130" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D130" t="s">
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F130" s="1">
         <v>46245</v>
@@ -5824,19 +5824,19 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B131" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C131" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D131" t="s">
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F131" s="1">
         <v>46245</v>
@@ -5844,19 +5844,19 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B132" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C132" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D132" t="s">
         <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F132" s="1">
         <v>46245</v>
@@ -5864,13 +5864,13 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B133" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C133" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D133" t="s">
         <v>9</v>
@@ -5887,10 +5887,10 @@
         <v>405</v>
       </c>
       <c r="B134" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C134" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D134" t="s">
         <v>9</v>
@@ -5907,16 +5907,16 @@
         <v>407</v>
       </c>
       <c r="B135" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C135" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D135" t="s">
         <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F135" s="1">
         <v>46245</v>
@@ -5924,19 +5924,19 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B136" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C136" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D136" t="s">
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F136" s="1">
         <v>46245</v>
@@ -5944,19 +5944,19 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B137" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C137" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D137" t="s">
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F137" s="1">
         <v>46245</v>
@@ -5964,19 +5964,19 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B138" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C138" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D138" t="s">
         <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F138" s="1">
         <v>46245</v>
@@ -5984,19 +5984,19 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B139" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C139" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D139" t="s">
         <v>9</v>
       </c>
       <c r="E139" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F139" s="1">
         <v>46245</v>
@@ -6004,19 +6004,19 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B140" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C140" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D140" t="s">
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F140" s="1">
         <v>46245</v>
@@ -6024,19 +6024,19 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B141" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C141" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D141" t="s">
         <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F141" s="1">
         <v>46245</v>
@@ -6044,13 +6044,13 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B142" t="s">
-        <v>428</v>
+        <v>22</v>
       </c>
       <c r="C142" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D142" t="s">
         <v>9</v>
@@ -6067,16 +6067,16 @@
         <v>430</v>
       </c>
       <c r="B143" t="s">
-        <v>25</v>
+        <v>431</v>
       </c>
       <c r="C143" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D143" t="s">
         <v>9</v>
       </c>
       <c r="E143" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F143" s="1">
         <v>46245</v>
@@ -6084,13 +6084,13 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B144" t="s">
-        <v>433</v>
+        <v>313</v>
       </c>
       <c r="C144" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D144" t="s">
         <v>9</v>
@@ -6107,16 +6107,16 @@
         <v>435</v>
       </c>
       <c r="B145" t="s">
-        <v>316</v>
+        <v>436</v>
       </c>
       <c r="C145" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D145" t="s">
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F145" s="1">
         <v>46245</v>
@@ -6124,13 +6124,13 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B146" t="s">
-        <v>438</v>
+        <v>104</v>
       </c>
       <c r="C146" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D146" t="s">
         <v>9</v>
@@ -6147,10 +6147,10 @@
         <v>440</v>
       </c>
       <c r="B147" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C147" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D147" t="s">
         <v>9</v>
@@ -6167,10 +6167,10 @@
         <v>442</v>
       </c>
       <c r="B148" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C148" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D148" t="s">
         <v>9</v>
@@ -6187,10 +6187,10 @@
         <v>444</v>
       </c>
       <c r="B149" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C149" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D149" t="s">
         <v>9</v>
@@ -6207,10 +6207,10 @@
         <v>446</v>
       </c>
       <c r="B150" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C150" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D150" t="s">
         <v>9</v>
@@ -6227,10 +6227,10 @@
         <v>448</v>
       </c>
       <c r="B151" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C151" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D151" t="s">
         <v>9</v>
@@ -6247,10 +6247,10 @@
         <v>450</v>
       </c>
       <c r="B152" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C152" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D152" t="s">
         <v>9</v>
@@ -6267,10 +6267,10 @@
         <v>452</v>
       </c>
       <c r="B153" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C153" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D153" t="s">
         <v>9</v>
@@ -6287,10 +6287,10 @@
         <v>454</v>
       </c>
       <c r="B154" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C154" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D154" t="s">
         <v>9</v>
@@ -6307,10 +6307,10 @@
         <v>456</v>
       </c>
       <c r="B155" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C155" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D155" t="s">
         <v>9</v>
@@ -6327,10 +6327,10 @@
         <v>458</v>
       </c>
       <c r="B156" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C156" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D156" t="s">
         <v>9</v>
@@ -6347,10 +6347,10 @@
         <v>460</v>
       </c>
       <c r="B157" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C157" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D157" t="s">
         <v>9</v>
@@ -6367,10 +6367,10 @@
         <v>462</v>
       </c>
       <c r="B158" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C158" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D158" t="s">
         <v>9</v>
@@ -6387,10 +6387,10 @@
         <v>464</v>
       </c>
       <c r="B159" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C159" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D159" t="s">
         <v>9</v>
@@ -6407,10 +6407,10 @@
         <v>466</v>
       </c>
       <c r="B160" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C160" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D160" t="s">
         <v>9</v>
@@ -6427,10 +6427,10 @@
         <v>468</v>
       </c>
       <c r="B161" t="s">
-        <v>107</v>
+        <v>211</v>
       </c>
       <c r="C161" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D161" t="s">
         <v>9</v>
@@ -6447,16 +6447,16 @@
         <v>470</v>
       </c>
       <c r="B162" t="s">
-        <v>214</v>
+        <v>289</v>
       </c>
       <c r="C162" t="s">
-        <v>371</v>
+        <v>471</v>
       </c>
       <c r="D162" t="s">
         <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F162" s="1">
         <v>46245</v>
@@ -6464,13 +6464,13 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B163" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C163" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D163" t="s">
         <v>9</v>
@@ -6487,10 +6487,10 @@
         <v>475</v>
       </c>
       <c r="B164" t="s">
-        <v>292</v>
+        <v>197</v>
       </c>
       <c r="C164" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
@@ -6507,16 +6507,16 @@
         <v>477</v>
       </c>
       <c r="B165" t="s">
-        <v>200</v>
+        <v>478</v>
       </c>
       <c r="C165" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F165" s="1">
         <v>46245</v>
@@ -6524,13 +6524,13 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B166" t="s">
-        <v>480</v>
+        <v>15</v>
       </c>
       <c r="C166" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D166" t="s">
         <v>9</v>
@@ -6547,10 +6547,10 @@
         <v>482</v>
       </c>
       <c r="B167" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C167" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D167" t="s">
         <v>9</v>
@@ -6567,16 +6567,16 @@
         <v>484</v>
       </c>
       <c r="B168" t="s">
-        <v>18</v>
+        <v>485</v>
       </c>
       <c r="C168" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D168" t="s">
         <v>9</v>
       </c>
       <c r="E168" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F168" s="1">
         <v>46245</v>
@@ -6584,13 +6584,13 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B169" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="C169" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D169" t="s">
         <v>9</v>
@@ -6607,10 +6607,10 @@
         <v>489</v>
       </c>
       <c r="B170" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C170" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D170" t="s">
         <v>9</v>
@@ -6627,16 +6627,16 @@
         <v>491</v>
       </c>
       <c r="B171" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="C171" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D171" t="s">
         <v>9</v>
       </c>
       <c r="E171" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F171" s="1">
         <v>46245</v>
@@ -6644,19 +6644,19 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B172" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C172" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D172" t="s">
         <v>9</v>
       </c>
       <c r="E172" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F172" s="1">
         <v>46245</v>
@@ -6664,19 +6664,19 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B173" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C173" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="D173" t="s">
         <v>9</v>
       </c>
       <c r="E173" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F173" s="1">
         <v>46245</v>
@@ -6684,19 +6684,19 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B174" t="s">
-        <v>500</v>
+        <v>327</v>
       </c>
       <c r="C174" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D174" t="s">
         <v>9</v>
       </c>
       <c r="E174" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F174" s="1">
         <v>46245</v>
@@ -6704,19 +6704,19 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B175" t="s">
-        <v>330</v>
+        <v>505</v>
       </c>
       <c r="C175" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D175" t="s">
         <v>9</v>
       </c>
       <c r="E175" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F175" s="1">
         <v>46245</v>
@@ -6724,19 +6724,19 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B176" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C176" t="s">
-        <v>508</v>
+        <v>16</v>
       </c>
       <c r="D176" t="s">
-        <v>9</v>
+        <v>510</v>
       </c>
       <c r="E176" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F176" s="1">
         <v>46245</v>
@@ -6744,19 +6744,19 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
+        <v>512</v>
+      </c>
+      <c r="B177" t="s">
+        <v>513</v>
+      </c>
+      <c r="C177" t="s">
+        <v>43</v>
+      </c>
+      <c r="D177" t="s">
         <v>510</v>
       </c>
-      <c r="B177" t="s">
-        <v>511</v>
-      </c>
-      <c r="C177" t="s">
-        <v>19</v>
-      </c>
-      <c r="D177" t="s">
-        <v>512</v>
-      </c>
       <c r="E177" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F177" s="1">
         <v>46245</v>
@@ -6764,19 +6764,19 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B178" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C178" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D178" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E178" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F178" s="1">
         <v>46245</v>
@@ -6784,19 +6784,19 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B179" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C179" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D179" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E179" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F179" s="1">
         <v>46245</v>
@@ -6804,19 +6804,19 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B180" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C180" t="s">
-        <v>73</v>
+        <v>218</v>
       </c>
       <c r="D180" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E180" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F180" s="1">
         <v>46245</v>
@@ -6824,19 +6824,19 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B181" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C181" t="s">
-        <v>221</v>
+        <v>526</v>
       </c>
       <c r="D181" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E181" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F181" s="1">
         <v>46245</v>
@@ -6844,19 +6844,19 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B182" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C182" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D182" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E182" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F182" s="1">
         <v>46245</v>
@@ -6864,19 +6864,19 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B183" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C183" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D183" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E183" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F183" s="1">
         <v>46245</v>
@@ -6884,19 +6884,19 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B184" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C184" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D184" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E184" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F184" s="1">
         <v>46245</v>
@@ -6904,19 +6904,19 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B185" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="C185" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D185" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E185" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F185" s="1">
         <v>46245</v>
@@ -6924,19 +6924,19 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B186" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="C186" t="s">
-        <v>543</v>
+        <v>16</v>
       </c>
       <c r="D186" t="s">
-        <v>512</v>
+        <v>545</v>
       </c>
       <c r="E186" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F186" s="1">
         <v>46245</v>
@@ -6944,19 +6944,19 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
+        <v>547</v>
+      </c>
+      <c r="B187" t="s">
+        <v>548</v>
+      </c>
+      <c r="C187" t="s">
+        <v>26</v>
+      </c>
+      <c r="D187" t="s">
         <v>545</v>
       </c>
-      <c r="B187" t="s">
-        <v>546</v>
-      </c>
-      <c r="C187" t="s">
-        <v>19</v>
-      </c>
-      <c r="D187" t="s">
-        <v>547</v>
-      </c>
       <c r="E187" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F187" s="1">
         <v>46245</v>
@@ -6964,19 +6964,19 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B188" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C188" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="D188" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E188" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F188" s="1">
         <v>46245</v>
@@ -6984,19 +6984,19 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B189" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C189" t="s">
-        <v>118</v>
+        <v>228</v>
       </c>
       <c r="D189" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E189" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F189" s="1">
         <v>46245</v>
@@ -7004,19 +7004,19 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B190" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C190" t="s">
-        <v>231</v>
+        <v>558</v>
       </c>
       <c r="D190" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E190" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F190" s="1">
         <v>46245</v>
@@ -7024,19 +7024,19 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B191" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="C191" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D191" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E191" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F191" s="1">
         <v>46245</v>
@@ -7044,19 +7044,19 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B192" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="C192" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D192" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E192" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F192" s="1">
         <v>46245</v>
@@ -7064,19 +7064,19 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B193" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C193" t="s">
-        <v>563</v>
+        <v>302</v>
       </c>
       <c r="D193" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E193" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F193" s="1">
         <v>46245</v>
@@ -7084,19 +7084,19 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B194" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C194" t="s">
-        <v>305</v>
+        <v>571</v>
       </c>
       <c r="D194" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E194" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F194" s="1">
         <v>46245</v>
@@ -7104,19 +7104,19 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B195" t="s">
-        <v>572</v>
+        <v>548</v>
       </c>
       <c r="C195" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D195" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E195" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F195" s="1">
         <v>46245</v>
@@ -7124,19 +7124,19 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B196" t="s">
-        <v>550</v>
+        <v>577</v>
       </c>
       <c r="C196" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D196" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E196" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F196" s="1">
         <v>46245</v>
@@ -7144,19 +7144,19 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B197" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C197" t="s">
-        <v>576</v>
+        <v>8</v>
       </c>
       <c r="D197" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
       <c r="E197" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F197" s="1">
         <v>46245</v>
@@ -7164,19 +7164,19 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
+        <v>583</v>
+      </c>
+      <c r="B198" t="s">
+        <v>584</v>
+      </c>
+      <c r="C198" t="s">
+        <v>33</v>
+      </c>
+      <c r="D198" t="s">
         <v>581</v>
       </c>
-      <c r="B198" t="s">
-        <v>582</v>
-      </c>
-      <c r="C198" t="s">
-        <v>8</v>
-      </c>
-      <c r="D198" t="s">
-        <v>583</v>
-      </c>
       <c r="E198" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F198" s="1">
         <v>46245</v>
@@ -7184,19 +7184,19 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B199" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C199" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D199" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E199" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F199" s="1">
         <v>46245</v>
@@ -7204,19 +7204,19 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B200" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C200" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D200" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E200" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F200" s="1">
         <v>46245</v>
@@ -7224,19 +7224,19 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B201" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C201" t="s">
-        <v>73</v>
+        <v>594</v>
       </c>
       <c r="D201" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E201" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F201" s="1">
         <v>46245</v>
@@ -7244,19 +7244,19 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B202" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C202" t="s">
-        <v>596</v>
+        <v>253</v>
       </c>
       <c r="D202" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E202" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F202" s="1">
         <v>46245</v>
@@ -7264,19 +7264,19 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B203" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="C203" t="s">
-        <v>256</v>
+        <v>600</v>
       </c>
       <c r="D203" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E203" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F203" s="1">
         <v>46245</v>
@@ -7284,19 +7284,19 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B204" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C204" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D204" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E204" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F204" s="1">
         <v>46245</v>
@@ -7304,19 +7304,19 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B205" t="s">
-        <v>595</v>
+        <v>548</v>
       </c>
       <c r="C205" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D205" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E205" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F205" s="1">
         <v>46245</v>
@@ -7324,19 +7324,16 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B206" t="s">
-        <v>550</v>
-      </c>
-      <c r="C206" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D206" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="E206" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="F206" s="1">
         <v>46245</v>
@@ -7344,13 +7341,13 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
+        <v>612</v>
+      </c>
+      <c r="B207" t="s">
+        <v>609</v>
+      </c>
+      <c r="D207" t="s">
         <v>610</v>
-      </c>
-      <c r="B207" t="s">
-        <v>611</v>
-      </c>
-      <c r="D207" t="s">
-        <v>612</v>
       </c>
       <c r="E207" t="s">
         <v>613</v>
@@ -7364,10 +7361,10 @@
         <v>614</v>
       </c>
       <c r="B208" t="s">
-        <v>611</v>
+        <v>49</v>
       </c>
       <c r="D208" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E208" t="s">
         <v>615</v>
@@ -7381,13 +7378,13 @@
         <v>616</v>
       </c>
       <c r="B209" t="s">
-        <v>52</v>
+        <v>617</v>
       </c>
       <c r="D209" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E209" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F209" s="1">
         <v>46245</v>
@@ -7395,16 +7392,16 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B210" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D210" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E210" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F210" s="1">
         <v>46245</v>
@@ -7412,16 +7409,16 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B211" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D211" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E211" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F211" s="1">
         <v>46245</v>
@@ -7429,16 +7426,16 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B212" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D212" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E212" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F212" s="1">
         <v>46245</v>
@@ -7446,16 +7443,16 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B213" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D213" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E213" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F213" s="1">
         <v>46245</v>
@@ -7463,16 +7460,16 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B214" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D214" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="E214" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F214" s="1">
         <v>46245</v>
@@ -7480,13 +7477,13 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B215" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D215" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E215" t="s">
         <v>635</v>
@@ -7500,13 +7497,13 @@
         <v>636</v>
       </c>
       <c r="B216" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D216" t="s">
-        <v>634</v>
+        <v>610</v>
       </c>
       <c r="E216" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F216" s="1">
         <v>46245</v>
@@ -7514,13 +7511,13 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B217" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="D217" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E217" t="s">
         <v>640</v>
@@ -7534,13 +7531,13 @@
         <v>641</v>
       </c>
       <c r="B218" t="s">
-        <v>628</v>
+        <v>642</v>
       </c>
       <c r="D218" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E218" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F218" s="1">
         <v>46245</v>
@@ -7548,16 +7545,16 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B219" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D219" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E219" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F219" s="1">
         <v>46245</v>
@@ -7565,13 +7562,13 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B220" t="s">
-        <v>647</v>
+        <v>25</v>
       </c>
       <c r="D220" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E220" t="s">
         <v>648</v>
@@ -7585,10 +7582,10 @@
         <v>649</v>
       </c>
       <c r="B221" t="s">
-        <v>28</v>
+        <v>623</v>
       </c>
       <c r="D221" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E221" t="s">
         <v>650</v>
@@ -7602,10 +7599,10 @@
         <v>651</v>
       </c>
       <c r="B222" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="D222" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E222" t="s">
         <v>652</v>
@@ -7619,13 +7616,13 @@
         <v>653</v>
       </c>
       <c r="B223" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
       <c r="D223" t="s">
-        <v>612</v>
+        <v>655</v>
       </c>
       <c r="E223" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F223" s="1">
         <v>46245</v>
@@ -7633,13 +7630,13 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
+        <v>657</v>
+      </c>
+      <c r="B224" t="s">
+        <v>654</v>
+      </c>
+      <c r="D224" t="s">
         <v>655</v>
-      </c>
-      <c r="B224" t="s">
-        <v>656</v>
-      </c>
-      <c r="D224" t="s">
-        <v>657</v>
       </c>
       <c r="E224" t="s">
         <v>658</v>
@@ -7653,10 +7650,10 @@
         <v>659</v>
       </c>
       <c r="B225" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D225" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E225" t="s">
         <v>660</v>
@@ -7670,10 +7667,10 @@
         <v>661</v>
       </c>
       <c r="B226" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D226" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E226" t="s">
         <v>662</v>
@@ -7687,10 +7684,10 @@
         <v>663</v>
       </c>
       <c r="B227" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D227" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E227" t="s">
         <v>664</v>
@@ -7704,10 +7701,10 @@
         <v>665</v>
       </c>
       <c r="B228" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D228" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E228" t="s">
         <v>666</v>
@@ -7721,10 +7718,10 @@
         <v>667</v>
       </c>
       <c r="B229" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D229" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E229" t="s">
         <v>668</v>
@@ -7738,10 +7735,10 @@
         <v>669</v>
       </c>
       <c r="B230" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D230" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E230" t="s">
         <v>670</v>
@@ -7755,10 +7752,10 @@
         <v>671</v>
       </c>
       <c r="B231" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D231" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E231" t="s">
         <v>672</v>
@@ -7775,7 +7772,7 @@
         <v>674</v>
       </c>
       <c r="D232" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E232" t="s">
         <v>675</v>
@@ -7789,10 +7786,10 @@
         <v>676</v>
       </c>
       <c r="B233" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D233" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E233" t="s">
         <v>677</v>
@@ -7806,10 +7803,10 @@
         <v>678</v>
       </c>
       <c r="B234" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D234" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E234" t="s">
         <v>679</v>
@@ -7826,7 +7823,7 @@
         <v>674</v>
       </c>
       <c r="D235" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E235" t="s">
         <v>681</v>
@@ -7843,7 +7840,7 @@
         <v>674</v>
       </c>
       <c r="D236" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E236" t="s">
         <v>683</v>
@@ -7857,10 +7854,10 @@
         <v>684</v>
       </c>
       <c r="B237" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D237" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E237" t="s">
         <v>685</v>
@@ -7874,10 +7871,10 @@
         <v>686</v>
       </c>
       <c r="B238" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D238" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E238" t="s">
         <v>687</v>
@@ -7891,10 +7888,10 @@
         <v>688</v>
       </c>
       <c r="B239" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D239" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E239" t="s">
         <v>689</v>
@@ -7908,10 +7905,10 @@
         <v>690</v>
       </c>
       <c r="B240" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D240" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E240" t="s">
         <v>691</v>
@@ -7925,10 +7922,10 @@
         <v>692</v>
       </c>
       <c r="B241" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D241" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E241" t="s">
         <v>693</v>
@@ -7942,10 +7939,10 @@
         <v>694</v>
       </c>
       <c r="B242" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D242" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E242" t="s">
         <v>695</v>
@@ -7959,10 +7956,10 @@
         <v>696</v>
       </c>
       <c r="B243" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D243" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E243" t="s">
         <v>697</v>
@@ -7976,10 +7973,10 @@
         <v>698</v>
       </c>
       <c r="B244" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D244" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E244" t="s">
         <v>699</v>
@@ -7993,10 +7990,10 @@
         <v>700</v>
       </c>
       <c r="B245" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D245" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E245" t="s">
         <v>701</v>
@@ -8013,7 +8010,7 @@
         <v>674</v>
       </c>
       <c r="D246" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E246" t="s">
         <v>703</v>
@@ -8027,10 +8024,10 @@
         <v>704</v>
       </c>
       <c r="B247" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D247" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E247" t="s">
         <v>705</v>
@@ -8044,10 +8041,10 @@
         <v>706</v>
       </c>
       <c r="B248" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D248" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E248" t="s">
         <v>707</v>
@@ -8061,10 +8058,10 @@
         <v>708</v>
       </c>
       <c r="B249" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D249" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E249" t="s">
         <v>709</v>
@@ -8078,10 +8075,10 @@
         <v>710</v>
       </c>
       <c r="B250" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D250" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E250" t="s">
         <v>711</v>
@@ -8095,10 +8092,10 @@
         <v>712</v>
       </c>
       <c r="B251" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D251" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E251" t="s">
         <v>713</v>
@@ -8302,7 +8299,7 @@
         <v>738</v>
       </c>
       <c r="C263" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D263" t="s">
         <v>739</v>
@@ -8322,7 +8319,7 @@
         <v>738</v>
       </c>
       <c r="C264" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D264" t="s">
         <v>739</v>
@@ -8342,7 +8339,7 @@
         <v>738</v>
       </c>
       <c r="C265" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D265" t="s">
         <v>739</v>
@@ -8362,7 +8359,7 @@
         <v>738</v>
       </c>
       <c r="C266" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D266" t="s">
         <v>739</v>
@@ -8382,7 +8379,7 @@
         <v>738</v>
       </c>
       <c r="C267" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D267" t="s">
         <v>739</v>
@@ -8402,7 +8399,7 @@
         <v>738</v>
       </c>
       <c r="C268" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D268" t="s">
         <v>739</v>
@@ -8422,7 +8419,7 @@
         <v>738</v>
       </c>
       <c r="C269" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D269" t="s">
         <v>739</v>
@@ -8442,7 +8439,7 @@
         <v>738</v>
       </c>
       <c r="C270" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D270" t="s">
         <v>739</v>
@@ -9411,7 +9408,7 @@
         <v>862</v>
       </c>
       <c r="B327" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D327" t="s">
         <v>863</v>
@@ -9462,7 +9459,7 @@
         <v>871</v>
       </c>
       <c r="B330" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D330" t="s">
         <v>863</v>
@@ -9516,7 +9513,7 @@
         <v>878</v>
       </c>
       <c r="C333" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D333" t="s">
         <v>879</v>
@@ -9536,7 +9533,7 @@
         <v>878</v>
       </c>
       <c r="C334" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D334" t="s">
         <v>879</v>
@@ -9556,7 +9553,7 @@
         <v>878</v>
       </c>
       <c r="C335" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D335" t="s">
         <v>879</v>
